--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Exercicio de tudo até agora.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Exercicio de tudo até agora.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
+  <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elios\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBD7982-3D54-44EE-A537-98DD30B96388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C054DA4-668E-45B9-B8C3-F04D4E9CB33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="647" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="647" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados_TI" sheetId="1" r:id="rId1"/>
@@ -25,29 +25,23 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'Tempo Resposta'!$A$18:$A$26</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">'Tempo Resposta'!$B$17</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'Tamanho Mb'!$B$15</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'Tamanho Mb'!$B$16:$B$22</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'Tamanho Mb'!$A$16:$A$22</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'Tamanho Mb'!$B$15</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'Tamanho Mb'!$B$16:$B$22</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">'Tempo Resposta'!$B$18:$B$26</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Tempo Resposta'!$A$18:$A$26</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Tempo Resposta'!$B$17</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Tempo Resposta'!$B$18:$B$26</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sessão!$A$25:$A$40</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sessão!$B$24</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sessão!$B$25:$B$40</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'Tamanho Mb'!$A$16:$A$22</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sessão!$A$25:$A$40</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sessão!$B$24</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sessão!$B$25:$B$40</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'Tamanho Mb'!$A$16:$A$22</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'Tamanho Mb'!$B$15</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'Tamanho Mb'!$B$16:$B$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="81" r:id="rId9"/>
-    <pivotCache cacheId="87" r:id="rId10"/>
-    <pivotCache cacheId="72" r:id="rId11"/>
-    <pivotCache cacheId="94" r:id="rId12"/>
-    <pivotCache cacheId="120" r:id="rId13"/>
-    <pivotCache cacheId="135" r:id="rId14"/>
-    <pivotCache cacheId="162" r:id="rId15"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="2" r:id="rId11"/>
+    <pivotCache cacheId="3" r:id="rId12"/>
+    <pivotCache cacheId="4" r:id="rId13"/>
+    <pivotCache cacheId="5" r:id="rId14"/>
+    <pivotCache cacheId="6" r:id="rId15"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -68,8 +62,45 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="57">
   <si>
     <t>ID</t>
   </si>
@@ -217,11 +248,38 @@
   <si>
     <t>Região</t>
   </si>
+  <si>
+    <t>Moda</t>
+  </si>
+  <si>
+    <t>Mediana</t>
+  </si>
+  <si>
+    <t>Variância</t>
+  </si>
+  <si>
+    <t>Desvio Padrão</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tempo Resposta</t>
+  </si>
+  <si>
+    <t>Requisições Sessão</t>
+  </si>
+  <si>
+    <t>Tamanho MB</t>
+  </si>
+  <si>
+    <t>Variáveis</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -259,7 +317,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -365,11 +423,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -378,28 +477,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -459,26 +543,42 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="52">
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -567,6 +667,27 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
@@ -583,12 +704,6 @@
     </dxf>
     <dxf>
       <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1689,6 +1804,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6444-47B5-A3C6-2919A4388BD1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1704,6 +1824,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6444-47B5-A3C6-2919A4388BD1}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2939,6 +3064,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-10FC-443F-9D31-1DF1EFD784B2}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2954,6 +3084,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-10FC-443F-9D31-1DF1EFD784B2}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -3778,6 +3913,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6856-4019-8F27-18276D8E81E6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3793,6 +3933,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6856-4019-8F27-18276D8E81E6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -3808,6 +3953,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-6856-4019-8F27-18276D8E81E6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -3823,6 +3973,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-6856-4019-8F27-18276D8E81E6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -4305,7 +4460,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="pt-BR"/>
-              <a:t>Tipo de Usuário</a:t>
+              <a:t>Região</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4683,6 +4838,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-3331-47D7-8924-0C6862CAB7F2}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -4698,6 +4858,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-3331-47D7-8924-0C6862CAB7F2}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -4713,6 +4878,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-3331-47D7-8924-0C6862CAB7F2}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -4933,10 +5103,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.8</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -4988,7 +5158,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{EA53EBFC-A627-44B6-B02A-A6E11CD5DEA4}" formatIdx="0">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.7</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>FS</cx:v>
             </cx:txData>
           </cx:tx>
@@ -5017,61 +5187,64 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.9</cx:f>
+        <cx:f>_xlchart.v1.6</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.11</cx:f>
+        <cx:f>_xlchart.v1.8</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
-        <cx:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" compatLnSpc="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr kumimoji="0" lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:uLnTx/>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Tamanho Mb</a:t>
-            </a:r>
-          </a:p>
-        </cx:rich>
+        <cx:txData>
+          <cx:v>Tamanho Mb</cx:v>
+        </cx:txData>
       </cx:tx>
+      <cx:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" compatLnSpc="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="0" lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Tamanho Mb</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
         <cx:series layoutId="clusteredColumn" uniqueId="{07246FBE-C4ED-4CEC-ADF7-C0DF1ED351E4}" formatIdx="0">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.10</cx:f>
+              <cx:f>_xlchart.v1.7</cx:f>
               <cx:v>FS</cx:v>
             </cx:txData>
           </cx:tx>
@@ -14417,16 +14590,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>85724</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -14441,8 +14614,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7537450" y="184150"/>
-          <a:ext cx="6419850" cy="5346700"/>
+          <a:off x="7210425" y="0"/>
+          <a:ext cx="10858500" cy="7515224"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14716,18 +14889,13 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="pt-BR" sz="1200" b="1">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr lvl="0"/>
+          <a:pPr lvl="0">
+            <a:lnSpc>
+              <a:spcPts val="1400"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:endParaRPr lang="pt-BR" sz="1200">
             <a:solidFill>
               <a:schemeClr val="dk1"/>
@@ -14799,6 +14967,142 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t>Na sua opnião qual gráfico  melhor representou os dados? Justifique.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R:</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Na Tempo Respota o gráfico de coluna representa melhor os dados pois mostra os dados de uma forma mais entendível e simples.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Na Requisições por Sessão eu também falaria que o gráfico de coluna representa de uma forma mais simples de entender comparado ao de linhas.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>No Tamanho Mb só tem o uso do histograma, porém ele representa de uma maneira bem simples de entender como o gráfico de coluna.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>No Tipo de Usuário eu prefiro os gráficos de barras e colunas por serem mais faceís de compreended, o gráfico de pizza é bom também mas não do mesmo jeito que os outros dois gráficos apresentam as informações.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>No da Região eu prefiro o gráfico de barras por causa que ele parece melhor em representar os dados.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>No da Prioridade eu também prefiro o de colunas por ser facíl de analisar.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>No de Status eu prefiro o de pizza porque ele representa de um jeito mais significativo para a enfrentação de um problema.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -15064,8 +15368,68 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
+            <a:t>R: Não existe moda por causa que não tem numeros repetidos dentro da sequência.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t> A média representa bem os dados? Justifique com base na dispersão.</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: Não exatamente, pois tem vários números</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> com valores grandes e pequenos que nem chegam perto dessa resposta.</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:endParaRPr lang="pt-BR" sz="1200">
@@ -15138,6 +15502,41 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
+            <a:t>R: São heterogêneos</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> pois não se existe outros números de mesmo valor dentro desses dados.</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1200">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t> </a:t>
           </a:r>
         </a:p>
@@ -15180,6 +15579,30 @@
         </a:p>
         <a:p>
           <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> Não, a maioria dos resultados deram números próximos um dos outros.</a:t>
+          </a:r>
           <a:endParaRPr lang="pt-BR" sz="1200" b="0">
             <a:solidFill>
               <a:schemeClr val="dk1"/>
@@ -15260,8 +15683,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3311525" y="203200"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="3213100" y="209550"/>
+              <a:ext cx="4356100" cy="2838450"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -15379,8 +15802,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3305175" y="406400"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="3190875" y="419100"/>
+              <a:ext cx="4572000" cy="2838450"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -15498,8 +15921,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3451225" y="304800"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="3355975" y="311150"/>
+              <a:ext cx="4572000" cy="2838450"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -20819,7 +21242,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BAE6BEF2-2551-46E7-AE50-4A4C60DCE74E}" name="Tabela dinâmica2" cacheId="81" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo Resposta">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BAE6BEF2-2551-46E7-AE50-4A4C60DCE74E}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo Resposta">
   <location ref="A3:D13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0">
@@ -21024,19 +21447,19 @@
     <dataField name="FA" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="47">
+    <format dxfId="51">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="50">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="49">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -21061,7 +21484,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C29BF07-BDDB-4534-AE0C-088EC7028C3F}" name="Tabela dinâmica12" cacheId="87" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Requisição por Sessão">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C29BF07-BDDB-4534-AE0C-088EC7028C3F}" name="Tabela dinâmica12" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Requisição por Sessão">
   <location ref="A3:D20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -21177,19 +21600,19 @@
     <dataField name="FA" fld="2" subtotal="count" showDataAs="runTotal" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="11">
-    <format dxfId="24">
+    <format dxfId="46">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="45">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="44">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -21198,19 +21621,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="41">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="40">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="39">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -21219,7 +21642,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="36">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -21242,7 +21665,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BFB16522-CBC0-4805-A711-F81BE2F8A4C7}" name="Tabela dinâmica20" cacheId="72" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tamanho Mb">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BFB16522-CBC0-4805-A711-F81BE2F8A4C7}" name="Tabela dinâmica20" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tamanho Mb">
   <location ref="A3:D11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -21324,16 +21747,16 @@
     <dataField name="FA" fld="3" subtotal="count" showDataAs="runTotal" baseField="3" baseItem="1"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="46">
+    <format dxfId="35">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="33">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="7">
@@ -21348,10 +21771,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -21362,16 +21785,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="40">
+    <format dxfId="29">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="27">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="7">
@@ -21386,10 +21809,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="36">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -21414,7 +21837,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{248CD6D2-190F-4CD1-BCD7-1378B9688E1F}" name="Tabela dinâmica28" cacheId="94" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tipo Usuário">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{248CD6D2-190F-4CD1-BCD7-1378B9688E1F}" name="Tabela dinâmica28" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tipo Usuário">
   <location ref="A3:D6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -21518,7 +21941,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F0DD972-7C08-484F-BF4D-38B843994521}" name="Tabela dinâmica40" cacheId="120" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Região">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F0DD972-7C08-484F-BF4D-38B843994521}" name="Tabela dinâmica40" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Região">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -21622,7 +22045,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A788C7CA-0BF4-4F9F-A7C1-447EAA1A8214}" name="Tabela dinâmica46" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Prioridade">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A788C7CA-0BF4-4F9F-A7C1-447EAA1A8214}" name="Tabela dinâmica46" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Prioridade">
   <location ref="A3:D7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -21730,7 +22153,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{323B8CD7-1EBF-4D0C-BC36-A5E1722D2E3F}" name="Tabela dinâmica58" cacheId="162" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{323B8CD7-1EBF-4D0C-BC36-A5E1722D2E3F}" name="Tabela dinâmica58" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
   <location ref="A3:D6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -21831,6 +22254,68 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>8</v>
+    <v>13</v>
+    <v>6</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22118,21 +22603,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetPr codeName="Planilha1"/>
+  <dimension ref="A1:Y61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.54296875" customWidth="1"/>
-    <col min="12" max="12" width="19.26953125" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" customWidth="1"/>
+    <col min="16" max="17" width="9.42578125" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22158,7 +22646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -22184,7 +22672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -22210,7 +22698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -22236,7 +22724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -22262,7 +22750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -22288,7 +22776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -22314,7 +22802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -22340,7 +22828,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -22366,7 +22854,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -22392,7 +22880,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -22418,7 +22906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -22444,7 +22932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -22470,7 +22958,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -22496,7 +22984,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -22522,7 +23010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -22548,7 +23036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -22574,7 +23062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -22600,7 +23088,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -22626,7 +23114,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -22652,7 +23140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -22678,7 +23166,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -22704,7 +23192,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -22730,7 +23218,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -22756,7 +23244,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -22782,7 +23270,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -22808,7 +23296,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -22834,7 +23322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -22860,7 +23348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -22886,7 +23374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -22912,7 +23400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -22938,7 +23426,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -22965,7 +23453,7 @@
       </c>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -22990,14 +23478,8 @@
       <c r="H33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="3">
-        <v>1</v>
-      </c>
-      <c r="N33" s="3">
-        <v>3</v>
-      </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -23023,7 +23505,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -23048,15 +23530,8 @@
       <c r="H35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J35" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="K35" s="5"/>
-      <c r="L35" s="6" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -23081,15 +23556,8 @@
       <c r="H36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K36" s="8"/>
-      <c r="L36" s="9" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -23114,15 +23582,8 @@
       <c r="H37" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J37" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="K37" s="8"/>
-      <c r="L37" s="9" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -23147,15 +23608,10 @@
       <c r="H38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J38" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="8"/>
-      <c r="L38" s="9" t="s">
-        <v>22</v>
-      </c>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -23180,15 +23636,8 @@
       <c r="H39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J39" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K39" s="8"/>
-      <c r="L39" s="9" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -23213,15 +23662,9 @@
       <c r="H40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J40" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="K40" s="8"/>
-      <c r="L40" s="9" t="s">
-        <v>19</v>
-      </c>
+      <c r="K40" s="36"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -23246,15 +23689,8 @@
       <c r="H41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J41" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="K41" s="8"/>
-      <c r="L41" s="9" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -23279,15 +23715,20 @@
       <c r="H42" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J42" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="12" t="s">
-        <v>19</v>
-      </c>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -23312,8 +23753,20 @@
       <c r="H43" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -23338,8 +23791,20 @@
       <c r="H44" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -23364,8 +23829,20 @@
       <c r="H45" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -23391,7 +23868,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -23416,8 +23893,14 @@
       <c r="H47" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J47" s="3">
+        <v>1</v>
+      </c>
+      <c r="N47" s="3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -23443,7 +23926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -23469,7 +23952,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -23494,8 +23977,39 @@
       <c r="H50" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J50" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="K50" s="31"/>
+      <c r="L50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N50" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="O50" s="32"/>
+      <c r="P50" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="U50" s="32"/>
+      <c r="V50" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="W50" s="32"/>
+      <c r="X50" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y50" s="32"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -23520,8 +24034,44 @@
       <c r="H51" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="J51" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="K51" s="27"/>
+      <c r="L51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N51" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="O51" s="32"/>
+      <c r="P51" s="32">
+        <f>AVERAGE(B2:B61)</f>
+        <v>207.8</v>
+      </c>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="34" t="e" cm="1">
+        <f t="array" ref="R51">_xlfn.MODE.MULT(B2:B61)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="S51" s="35"/>
+      <c r="T51" s="32">
+        <f>MEDIAN(B2:B61)</f>
+        <v>189</v>
+      </c>
+      <c r="U51" s="32"/>
+      <c r="V51" s="33">
+        <f>_xlfn.VAR.S(B2:B61)</f>
+        <v>4895.2135593220355</v>
+      </c>
+      <c r="W51" s="33"/>
+      <c r="X51" s="33">
+        <f>_xlfn.STDEV.S(B2:B61)</f>
+        <v>69.965802784803628</v>
+      </c>
+      <c r="Y51" s="33"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -23546,8 +24096,44 @@
       <c r="H52" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J52" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="K52" s="27"/>
+      <c r="L52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N52" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="O52" s="32"/>
+      <c r="P52" s="33">
+        <f>AVERAGE(C2:C61)</f>
+        <v>8.4833333333333325</v>
+      </c>
+      <c r="Q52" s="33"/>
+      <c r="R52" s="32" cm="1">
+        <f t="array" ref="R52">_xlfn.MODE.MULT(C2:C61)</f>
+        <v>7</v>
+      </c>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32">
+        <f>MEDIAN(C2:C61)</f>
+        <v>8</v>
+      </c>
+      <c r="U52" s="32"/>
+      <c r="V52" s="33">
+        <f>_xlfn.VAR.S(C2:C61)</f>
+        <v>17.135310734463282</v>
+      </c>
+      <c r="W52" s="33"/>
+      <c r="X52" s="33">
+        <f>_xlfn.STDEV.S(C2:C61)</f>
+        <v>4.1394819403475216</v>
+      </c>
+      <c r="Y52" s="33"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -23572,8 +24158,44 @@
       <c r="H53" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J53" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="K53" s="27"/>
+      <c r="L53" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N53" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="O53" s="32"/>
+      <c r="P53" s="33">
+        <f>AVERAGE(D2:D61)</f>
+        <v>2.9283333333333332</v>
+      </c>
+      <c r="Q53" s="33"/>
+      <c r="R53" s="34" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="R53" ca="1">_xlfn.MODE.MULT(D2:D61)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S53" s="35"/>
+      <c r="T53" s="32">
+        <f>MEDIAN(D2:D61)</f>
+        <v>2.5</v>
+      </c>
+      <c r="U53" s="32"/>
+      <c r="V53" s="33">
+        <f>_xlfn.VAR.S(D2:D61)</f>
+        <v>3.4322344632768327</v>
+      </c>
+      <c r="W53" s="33"/>
+      <c r="X53" s="33">
+        <f>_xlfn.STDEV.S(D2:D61)</f>
+        <v>1.8526290679131732</v>
+      </c>
+      <c r="Y53" s="33"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -23598,8 +24220,15 @@
       <c r="H54" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="J54" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="27"/>
+      <c r="L54" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -23624,8 +24253,15 @@
       <c r="H55" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J55" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="K55" s="27"/>
+      <c r="L55" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -23650,8 +24286,15 @@
       <c r="H56" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="J56" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="K56" s="27"/>
+      <c r="L56" s="6" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -23676,8 +24319,15 @@
       <c r="H57" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J57" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="K57" s="29"/>
+      <c r="L57" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -23703,7 +24353,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -23729,7 +24379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -23755,7 +24405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -23782,50 +24432,76 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
+  <mergeCells count="32">
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="X51:Y51"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="X53:Y53"/>
+    <mergeCell ref="T53:U53"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="V53:W53"/>
+    <mergeCell ref="V50:W50"/>
+    <mergeCell ref="X50:Y50"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="J53:K53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ACA1C58-9D91-4693-8874-FBEE7ADA22AA}">
+  <sheetPr codeName="Planilha2"/>
   <dimension ref="A3:F52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="16" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="29" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="37" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="43" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="16" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="1.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="29" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="1.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="37" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="1.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="43" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="1.85546875" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -23838,307 +24514,307 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>12</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="10">
         <v>0.2</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>12</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="10">
         <v>0.2</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>10</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="10">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <v>6</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="10">
         <v>0.1</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="9">
         <v>6</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="10">
         <v>0.1</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="9">
         <v>4</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="10">
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="9">
         <v>6</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="10">
         <v>0.1</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="9">
         <v>3</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="10">
         <v>0.05</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="9">
         <v>1</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="10">
         <v>1.6666666666666666E-2</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="9">
         <v>60</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="10">
         <v>1</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="9">
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="16" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="17" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="13">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C36" s="22"/>
+      <c r="D36" s="23"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C37" s="27"/>
-      <c r="D37" s="28"/>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C37" s="22"/>
+      <c r="D37" s="23"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C38" s="27"/>
-      <c r="D38" s="28"/>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C38" s="22"/>
+      <c r="D38" s="23"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C39" s="27"/>
-      <c r="D39" s="28"/>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C39" s="22"/>
+      <c r="D39" s="23"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C40" s="27"/>
-      <c r="D40" s="28"/>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C40" s="22"/>
+      <c r="D40" s="23"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C41" s="27"/>
-      <c r="D41" s="28"/>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C41" s="22"/>
+      <c r="D41" s="23"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="29"/>
-      <c r="B42" s="30"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="28"/>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+      <c r="B42" s="25"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="23"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E43" s="27"/>
-      <c r="F43" s="28"/>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E43" s="22"/>
+      <c r="F43" s="23"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E44" s="27"/>
-      <c r="F44" s="28"/>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E44" s="22"/>
+      <c r="F44" s="23"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E45" s="27"/>
-      <c r="F45" s="28"/>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E45" s="22"/>
+      <c r="F45" s="23"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E46" s="27"/>
-      <c r="F46" s="28"/>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E46" s="22"/>
+      <c r="F46" s="23"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E47" s="27"/>
-      <c r="F47" s="28"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="22"/>
+      <c r="F47" s="23"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E48" s="27"/>
-      <c r="F48" s="28"/>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E48" s="22"/>
+      <c r="F48" s="23"/>
     </row>
-    <row r="49" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E49" s="27"/>
-      <c r="F49" s="28"/>
+    <row r="49" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E49" s="22"/>
+      <c r="F49" s="23"/>
     </row>
-    <row r="50" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E50" s="27"/>
-      <c r="F50" s="28"/>
+    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E50" s="22"/>
+      <c r="F50" s="23"/>
     </row>
-    <row r="51" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E51" s="27"/>
-      <c r="F51" s="28"/>
+    <row r="51" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E51" s="22"/>
+      <c r="F51" s="23"/>
     </row>
-    <row r="52" spans="5:6" x14ac:dyDescent="0.35">
-      <c r="E52" s="27"/>
-      <c r="F52" s="28"/>
+    <row r="52" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E52" s="22"/>
+      <c r="F52" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -24148,406 +24824,407 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{685F8683-9FF2-4AB3-9FF9-EB87E5A7F84B}">
+  <sheetPr codeName="Planilha3"/>
   <dimension ref="A3:D41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="20">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
         <v>2</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="16">
         <v>3</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="17">
         <v>0.05</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="20">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
         <v>3</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="16">
         <v>5</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="17">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="16">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="20">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
         <v>4</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="16">
         <v>5</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="17">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="16">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="20">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
         <v>5</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="16">
         <v>4</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="17">
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="16">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="20">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="16">
         <v>5</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="17">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="16">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="20">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
         <v>7</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="16">
         <v>6</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="17">
         <v>0.1</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="16">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="20">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
         <v>8</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="16">
         <v>4</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="17">
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="16">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="20">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
         <v>9</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="16">
         <v>3</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="17">
         <v>0.05</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="16">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="20">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
         <v>10</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="16">
         <v>4</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="17">
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="16">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="20">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
         <v>11</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="16">
         <v>4</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="17">
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="16">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="20">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
         <v>12</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="16">
         <v>4</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="17">
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="16">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="20">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
         <v>13</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="16">
         <v>5</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="17">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="16">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="20">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
         <v>14</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="16">
         <v>4</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="17">
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="16">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="20">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
         <v>15</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="16">
         <v>2</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="17">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="16">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="20">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="15">
         <v>16</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="16">
         <v>1</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="17">
         <v>1.6666666666666666E-2</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="16">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="20">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
         <v>18</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="16">
         <v>1</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="17">
         <v>1.6666666666666666E-2</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="16">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="20" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="16">
         <v>60</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="17">
         <v>1</v>
       </c>
-      <c r="D20" s="21"/>
+      <c r="D20" s="16"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="20">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="15">
         <v>2</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="20">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="15">
         <v>3</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="20">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="15">
         <v>4</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="20">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
         <v>5</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="16">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="20">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="15">
         <v>6</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="20">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="15">
         <v>7</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="16">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="20">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="15">
         <v>8</v>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="16">
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="20">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="15">
         <v>9</v>
       </c>
-      <c r="B32" s="21">
+      <c r="B32" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="20">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="15">
         <v>10</v>
       </c>
-      <c r="B33" s="21">
+      <c r="B33" s="16">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="20">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="15">
         <v>11</v>
       </c>
-      <c r="B34" s="21">
+      <c r="B34" s="16">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="20">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="15">
         <v>12</v>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="16">
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="20">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="15">
         <v>13</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="16">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="20">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="15">
         <v>14</v>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="16">
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="20">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="15">
         <v>15</v>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="20">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="15">
         <v>16</v>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="20">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="15">
         <v>18</v>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="24" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="20">
         <v>60</v>
       </c>
     </row>
@@ -24559,208 +25236,209 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A2EACB-222A-43C4-B6B8-BE010F23FC67}">
+  <sheetPr codeName="Planilha4"/>
   <dimension ref="A3:D23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="16">
         <v>18</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="17">
         <v>0.3</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="16">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="16">
         <v>11</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="17">
         <v>0.18333333333333332</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="16">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="16">
         <v>8</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="17">
         <v>0.13333333333333333</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="16">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="16">
         <v>8</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="17">
         <v>0.13333333333333333</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="16">
         <v>7</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="17">
         <v>0.11666666666666667</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="16">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="16">
         <v>6</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="17">
         <v>0.1</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="16">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="20" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="16">
         <v>2</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="17">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="16">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="16">
         <v>60</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="17">
         <v>1</v>
       </c>
-      <c r="D11" s="21"/>
+      <c r="D11" s="16"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="20" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="16">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="20" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="16">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="20" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="16">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="20" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="16">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="20" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="16">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="20" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="16">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="20" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="24" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="20">
         <v>60</v>
       </c>
     </row>
@@ -24772,17 +25450,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE94ACBA-5F69-4911-8427-0D54C30D4C0E}">
+  <sheetPr codeName="Planilha5"/>
   <dimension ref="A3:D12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -24795,75 +25474,75 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>33</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>27</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="10">
         <v>0.45</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>60</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="9"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="9">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="9">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="13">
         <v>60</v>
       </c>
     </row>
@@ -24875,17 +25554,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10730F53-1099-459F-BE17-73BB8AB9D61F}">
+  <sheetPr codeName="Planilha6"/>
   <dimension ref="A3:D16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -24898,119 +25578,119 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>10</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="10">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>10</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="10">
         <v>0.16666666666666666</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>22</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="10">
         <v>0.36666666666666664</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="9">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <v>18</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="10">
         <v>0.3</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="9">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="9">
         <v>60</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="9"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="9">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="9">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="17" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="13">
         <v>60</v>
       </c>
     </row>
@@ -25022,17 +25702,18 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADF40B5-799D-49EF-84DA-81B27C3CC8B3}">
+  <sheetPr codeName="Planilha7"/>
   <dimension ref="A3:D14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -25045,97 +25726,97 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>15</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="10">
         <v>0.25</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>25</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>20</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="9">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="9">
         <v>60</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="10">
         <v>1</v>
       </c>
-      <c r="D7" s="14"/>
+      <c r="D7" s="9"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="9">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="9">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="17" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="13">
         <v>60</v>
       </c>
     </row>
@@ -25147,17 +25828,18 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81FF32B4-D917-47CD-8634-6912E0CE5486}">
+  <sheetPr codeName="Planilha8"/>
   <dimension ref="A3:D12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -25170,75 +25852,75 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="9">
         <v>18</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="10">
         <v>0.3</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="9">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="9">
         <v>42</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="10">
         <v>0.7</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="9">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="9">
         <v>60</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="9"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="9">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="9">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="13">
         <v>60</v>
       </c>
     </row>

--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Exercicio de tudo até agora.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Exercicio de tudo até agora.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elios\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C054DA4-668E-45B9-B8C3-F04D4E9CB33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118F831C-1CED-460B-9244-1662C794FF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="647" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="647" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados_TI" sheetId="1" r:id="rId1"/>
@@ -63,10 +63,9 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -77,25 +76,11 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-  </valueMetadata>
 </metadata>
 </file>
 
@@ -278,7 +263,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -468,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -543,10 +528,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -555,25 +558,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15514,7 +15501,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> pois não se existe outros números de mesmo valor dentro desses dados.</a:t>
+            <a:t> pois a diferença entre a média e o desvio padrão é grande.</a:t>
           </a:r>
           <a:endParaRPr lang="pt-BR" sz="1200">
             <a:solidFill>
@@ -15683,8 +15670,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3213100" y="209550"/>
-              <a:ext cx="4356100" cy="2838450"/>
+              <a:off x="3311525" y="203200"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -15802,8 +15789,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3190875" y="419100"/>
-              <a:ext cx="4572000" cy="2838450"/>
+              <a:off x="3305175" y="406400"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -15921,8 +15908,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3355975" y="311150"/>
-              <a:ext cx="4572000" cy="2838450"/>
+              <a:off x="3444875" y="304800"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22256,68 +22243,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>8</v>
-    <v>13</v>
-    <v>6</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_error">
-    <k n="colOffset" t="i"/>
-    <k n="errorType" t="i"/>
-    <k n="rwOffset" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -22604,23 +22529,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:Y61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Y66"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" customWidth="1"/>
-    <col min="16" max="17" width="9.42578125" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.54296875" customWidth="1"/>
+    <col min="12" max="12" width="20.453125" customWidth="1"/>
+    <col min="16" max="17" width="9.453125" customWidth="1"/>
+    <col min="19" max="19" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22646,7 +22571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -22672,7 +22597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -22698,7 +22623,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -22724,7 +22649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -22750,7 +22675,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -22776,7 +22701,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -22802,7 +22727,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -22828,7 +22753,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -22854,7 +22779,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -22880,7 +22805,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -22906,7 +22831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -22932,7 +22857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -22958,7 +22883,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -22984,7 +22909,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -23010,7 +22935,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -23036,7 +22961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -23062,7 +22987,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -23088,7 +23013,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -23114,7 +23039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -23140,7 +23065,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -23166,7 +23091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -23192,7 +23117,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -23218,7 +23143,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -23244,7 +23169,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -23270,7 +23195,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -23296,7 +23221,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -23322,7 +23247,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -23348,7 +23273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -23374,7 +23299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -23400,7 +23325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -23426,7 +23351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -23453,7 +23378,7 @@
       </c>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -23479,7 +23404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -23505,7 +23430,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -23531,7 +23456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -23557,7 +23482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -23583,7 +23508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -23611,7 +23536,7 @@
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -23637,7 +23562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -23662,9 +23587,9 @@
       <c r="H40" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K40" s="36"/>
+      <c r="K40" s="26"/>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -23690,7 +23615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -23728,7 +23653,7 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -23766,7 +23691,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -23804,7 +23729,7 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -23842,7 +23767,7 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -23868,7 +23793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -23900,7 +23825,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -23926,7 +23851,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -23952,7 +23877,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -23977,39 +23902,39 @@
       <c r="H50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J50" s="30" t="s">
+      <c r="J50" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="K50" s="31"/>
+      <c r="K50" s="30"/>
       <c r="L50" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N50" s="32" t="s">
+      <c r="N50" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="O50" s="32"/>
-      <c r="P50" s="32" t="s">
+      <c r="O50" s="33"/>
+      <c r="P50" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="Q50" s="32"/>
-      <c r="R50" s="32" t="s">
+      <c r="Q50" s="33"/>
+      <c r="R50" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="S50" s="32"/>
-      <c r="T50" s="32" t="s">
+      <c r="S50" s="33"/>
+      <c r="T50" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="U50" s="32"/>
-      <c r="V50" s="32" t="s">
+      <c r="U50" s="33"/>
+      <c r="V50" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="W50" s="32"/>
-      <c r="X50" s="32" t="s">
+      <c r="W50" s="33"/>
+      <c r="X50" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="Y50" s="32"/>
+      <c r="Y50" s="33"/>
     </row>
-    <row r="51" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -24034,44 +23959,44 @@
       <c r="H51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="26" t="s">
+      <c r="J51" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="K51" s="27"/>
+      <c r="K51" s="32"/>
       <c r="L51" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N51" s="32" t="s">
+      <c r="N51" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="O51" s="32"/>
-      <c r="P51" s="32">
+      <c r="O51" s="33"/>
+      <c r="P51" s="33">
         <f>AVERAGE(B2:B61)</f>
         <v>207.8</v>
       </c>
-      <c r="Q51" s="32"/>
+      <c r="Q51" s="33"/>
       <c r="R51" s="34" t="e" cm="1">
         <f t="array" ref="R51">_xlfn.MODE.MULT(B2:B61)</f>
         <v>#N/A</v>
       </c>
       <c r="S51" s="35"/>
-      <c r="T51" s="32">
+      <c r="T51" s="33">
         <f>MEDIAN(B2:B61)</f>
         <v>189</v>
       </c>
-      <c r="U51" s="32"/>
-      <c r="V51" s="33">
+      <c r="U51" s="33"/>
+      <c r="V51" s="38">
         <f>_xlfn.VAR.S(B2:B61)</f>
         <v>4895.2135593220355</v>
       </c>
-      <c r="W51" s="33"/>
-      <c r="X51" s="33">
+      <c r="W51" s="38"/>
+      <c r="X51" s="38">
         <f>_xlfn.STDEV.S(B2:B61)</f>
         <v>69.965802784803628</v>
       </c>
-      <c r="Y51" s="33"/>
+      <c r="Y51" s="38"/>
     </row>
-    <row r="52" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -24096,44 +24021,44 @@
       <c r="H52" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J52" s="26" t="s">
+      <c r="J52" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="K52" s="27"/>
+      <c r="K52" s="32"/>
       <c r="L52" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N52" s="32" t="s">
+      <c r="N52" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="O52" s="32"/>
-      <c r="P52" s="33">
+      <c r="O52" s="33"/>
+      <c r="P52" s="38">
         <f>AVERAGE(C2:C61)</f>
         <v>8.4833333333333325</v>
       </c>
-      <c r="Q52" s="33"/>
-      <c r="R52" s="32" cm="1">
+      <c r="Q52" s="38"/>
+      <c r="R52" s="33" cm="1">
         <f t="array" ref="R52">_xlfn.MODE.MULT(C2:C61)</f>
         <v>7</v>
       </c>
-      <c r="S52" s="32"/>
-      <c r="T52" s="32">
+      <c r="S52" s="33"/>
+      <c r="T52" s="33">
         <f>MEDIAN(C2:C61)</f>
         <v>8</v>
       </c>
-      <c r="U52" s="32"/>
-      <c r="V52" s="33">
+      <c r="U52" s="33"/>
+      <c r="V52" s="38">
         <f>_xlfn.VAR.S(C2:C61)</f>
         <v>17.135310734463282</v>
       </c>
-      <c r="W52" s="33"/>
-      <c r="X52" s="33">
+      <c r="W52" s="38"/>
+      <c r="X52" s="38">
         <f>_xlfn.STDEV.S(C2:C61)</f>
         <v>4.1394819403475216</v>
       </c>
-      <c r="Y52" s="33"/>
+      <c r="Y52" s="38"/>
     </row>
-    <row r="53" spans="1:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -24158,44 +24083,44 @@
       <c r="H53" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J53" s="26" t="s">
+      <c r="J53" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="K53" s="27"/>
+      <c r="K53" s="32"/>
       <c r="L53" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N53" s="32" t="s">
+      <c r="N53" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="O53" s="32"/>
-      <c r="P53" s="33">
+      <c r="O53" s="33"/>
+      <c r="P53" s="38">
         <f>AVERAGE(D2:D61)</f>
         <v>2.9283333333333332</v>
       </c>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="34" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="R53" ca="1">_xlfn.MODE.MULT(D2:D61)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S53" s="35"/>
-      <c r="T53" s="32">
+      <c r="Q53" s="38"/>
+      <c r="R53" s="27" cm="1">
+        <f t="array" ref="R53:R66">_xlfn.MODE.MULT(D2:D61)</f>
+        <v>1.2</v>
+      </c>
+      <c r="S53" s="28"/>
+      <c r="T53" s="33">
         <f>MEDIAN(D2:D61)</f>
         <v>2.5</v>
       </c>
-      <c r="U53" s="32"/>
-      <c r="V53" s="33">
+      <c r="U53" s="33"/>
+      <c r="V53" s="38">
         <f>_xlfn.VAR.S(D2:D61)</f>
         <v>3.4322344632768327</v>
       </c>
-      <c r="W53" s="33"/>
-      <c r="X53" s="33">
+      <c r="W53" s="38"/>
+      <c r="X53" s="38">
         <f>_xlfn.STDEV.S(D2:D61)</f>
         <v>1.8526290679131732</v>
       </c>
-      <c r="Y53" s="33"/>
+      <c r="Y53" s="38"/>
     </row>
-    <row r="54" spans="1:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -24220,15 +24145,18 @@
       <c r="H54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J54" s="26" t="s">
+      <c r="J54" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="27"/>
+      <c r="K54" s="32"/>
       <c r="L54" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="R54">
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -24253,15 +24181,18 @@
       <c r="H55" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J55" s="26" t="s">
+      <c r="J55" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="K55" s="27"/>
+      <c r="K55" s="32"/>
       <c r="L55" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="R55">
+        <v>2</v>
+      </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -24286,15 +24217,18 @@
       <c r="H56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J56" s="26" t="s">
+      <c r="J56" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="K56" s="27"/>
+      <c r="K56" s="32"/>
       <c r="L56" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="R56">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -24319,15 +24253,18 @@
       <c r="H57" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J57" s="28" t="s">
+      <c r="J57" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="K57" s="29"/>
+      <c r="K57" s="37"/>
       <c r="L57" s="7" t="s">
         <v>19</v>
       </c>
+      <c r="R57">
+        <v>1.3</v>
+      </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -24352,8 +24289,11 @@
       <c r="H58" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="R58">
+        <v>2.5</v>
+      </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -24378,8 +24318,11 @@
       <c r="H59" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="R59">
+        <v>2.2000000000000002</v>
+      </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -24404,8 +24347,11 @@
       <c r="H60" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="R60">
+        <v>1.8</v>
+      </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -24430,9 +24376,40 @@
       <c r="H61" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="R62">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="R63">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="R64">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="65" spans="18:18" x14ac:dyDescent="0.35">
+      <c r="R65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="18:18" x14ac:dyDescent="0.35">
+      <c r="R66">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="31">
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J57:K57"/>
     <mergeCell ref="X52:Y52"/>
     <mergeCell ref="X51:Y51"/>
     <mergeCell ref="N50:O50"/>
@@ -24447,18 +24424,14 @@
     <mergeCell ref="N52:O52"/>
     <mergeCell ref="N53:O53"/>
     <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="J57:K57"/>
     <mergeCell ref="P50:Q50"/>
     <mergeCell ref="R50:S50"/>
     <mergeCell ref="T50:U50"/>
     <mergeCell ref="T51:U51"/>
     <mergeCell ref="T52:U52"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="P52:Q52"/>
     <mergeCell ref="J50:K50"/>
     <mergeCell ref="J51:K51"/>
     <mergeCell ref="J52:K52"/>
@@ -24476,31 +24449,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ACA1C58-9D91-4693-8874-FBEE7ADA22AA}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A3:F52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="16" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="1.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="1.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="29" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="1.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="37" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="1.85546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="43" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="1.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="16" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="29" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="37" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="43" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="1.81640625" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>25</v>
       </c>
@@ -24514,7 +24487,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -24528,7 +24501,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
@@ -24542,7 +24515,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
@@ -24556,7 +24529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -24570,7 +24543,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -24584,7 +24557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
@@ -24598,7 +24571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
@@ -24612,7 +24585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -24626,7 +24599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
@@ -24640,7 +24613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -24654,7 +24627,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -24662,7 +24635,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>37</v>
       </c>
@@ -24670,7 +24643,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>38</v>
       </c>
@@ -24678,7 +24651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -24686,7 +24659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -24694,7 +24667,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -24702,7 +24675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
@@ -24710,7 +24683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>43</v>
       </c>
@@ -24718,7 +24691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>44</v>
       </c>
@@ -24726,7 +24699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>45</v>
       </c>
@@ -24734,7 +24707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>24</v>
       </c>
@@ -24742,77 +24715,77 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C35" s="21"/>
       <c r="D35" s="21"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C36" s="22"/>
       <c r="D36" s="23"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C37" s="22"/>
       <c r="D37" s="23"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C38" s="22"/>
       <c r="D38" s="23"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C39" s="22"/>
       <c r="D39" s="23"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C40" s="22"/>
       <c r="D40" s="23"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C41" s="22"/>
       <c r="D41" s="23"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="24"/>
       <c r="B42" s="25"/>
       <c r="E42" s="22"/>
       <c r="F42" s="23"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E43" s="22"/>
       <c r="F43" s="23"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E44" s="22"/>
       <c r="F44" s="23"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E45" s="22"/>
       <c r="F45" s="23"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E46" s="22"/>
       <c r="F46" s="23"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E47" s="22"/>
       <c r="F47" s="23"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E48" s="22"/>
       <c r="F48" s="23"/>
     </row>
-    <row r="49" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:6" x14ac:dyDescent="0.35">
       <c r="E49" s="22"/>
       <c r="F49" s="23"/>
     </row>
-    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:6" x14ac:dyDescent="0.35">
       <c r="E50" s="22"/>
       <c r="F50" s="23"/>
     </row>
-    <row r="51" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:6" x14ac:dyDescent="0.35">
       <c r="E51" s="22"/>
       <c r="F51" s="23"/>
     </row>
-    <row r="52" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:6" x14ac:dyDescent="0.35">
       <c r="E52" s="22"/>
       <c r="F52" s="23"/>
     </row>
@@ -24826,15 +24799,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{685F8683-9FF2-4AB3-9FF9-EB87E5A7F84B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A3:D41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>29</v>
       </c>
@@ -24848,7 +24821,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="15">
         <v>2</v>
       </c>
@@ -24862,7 +24835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="15">
         <v>3</v>
       </c>
@@ -24876,7 +24849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="15">
         <v>4</v>
       </c>
@@ -24890,7 +24863,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="15">
         <v>5</v>
       </c>
@@ -24904,7 +24877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="15">
         <v>6</v>
       </c>
@@ -24918,7 +24891,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="15">
         <v>7</v>
       </c>
@@ -24932,7 +24905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="15">
         <v>8</v>
       </c>
@@ -24946,7 +24919,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="15">
         <v>9</v>
       </c>
@@ -24960,7 +24933,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="15">
         <v>10</v>
       </c>
@@ -24974,7 +24947,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="15">
         <v>11</v>
       </c>
@@ -24988,7 +24961,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="15">
         <v>12</v>
       </c>
@@ -25002,7 +24975,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="15">
         <v>13</v>
       </c>
@@ -25016,7 +24989,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="15">
         <v>14</v>
       </c>
@@ -25030,7 +25003,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="15">
         <v>15</v>
       </c>
@@ -25044,7 +25017,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="15">
         <v>16</v>
       </c>
@@ -25058,7 +25031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="15">
         <v>18</v>
       </c>
@@ -25072,7 +25045,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>24</v>
       </c>
@@ -25084,7 +25057,7 @@
       </c>
       <c r="D20" s="16"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="18" t="s">
         <v>29</v>
       </c>
@@ -25092,7 +25065,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="15">
         <v>2</v>
       </c>
@@ -25100,7 +25073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="15">
         <v>3</v>
       </c>
@@ -25108,7 +25081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="15">
         <v>4</v>
       </c>
@@ -25116,7 +25089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="15">
         <v>5</v>
       </c>
@@ -25124,7 +25097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="15">
         <v>6</v>
       </c>
@@ -25132,7 +25105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="15">
         <v>7</v>
       </c>
@@ -25140,7 +25113,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="15">
         <v>8</v>
       </c>
@@ -25148,7 +25121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="15">
         <v>9</v>
       </c>
@@ -25156,7 +25129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="15">
         <v>10</v>
       </c>
@@ -25164,7 +25137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="15">
         <v>11</v>
       </c>
@@ -25172,7 +25145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="15">
         <v>12</v>
       </c>
@@ -25180,7 +25153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="15">
         <v>13</v>
       </c>
@@ -25188,7 +25161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="15">
         <v>14</v>
       </c>
@@ -25196,7 +25169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="15">
         <v>15</v>
       </c>
@@ -25204,7 +25177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="15">
         <v>16</v>
       </c>
@@ -25212,7 +25185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="15">
         <v>18</v>
       </c>
@@ -25220,7 +25193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="19" t="s">
         <v>24</v>
       </c>
@@ -25238,15 +25211,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A2EACB-222A-43C4-B6B8-BE010F23FC67}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A3:D23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>46</v>
       </c>
@@ -25260,7 +25233,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>30</v>
       </c>
@@ -25274,7 +25247,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>31</v>
       </c>
@@ -25288,7 +25261,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>32</v>
       </c>
@@ -25302,7 +25275,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>33</v>
       </c>
@@ -25316,7 +25289,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>34</v>
       </c>
@@ -25330,7 +25303,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>35</v>
       </c>
@@ -25344,7 +25317,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>36</v>
       </c>
@@ -25358,7 +25331,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>24</v>
       </c>
@@ -25370,7 +25343,7 @@
       </c>
       <c r="D11" s="16"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
         <v>23</v>
       </c>
@@ -25378,7 +25351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>30</v>
       </c>
@@ -25386,7 +25359,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>31</v>
       </c>
@@ -25394,7 +25367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>32</v>
       </c>
@@ -25402,7 +25375,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>33</v>
       </c>
@@ -25410,7 +25383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>34</v>
       </c>
@@ -25418,7 +25391,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
         <v>35</v>
       </c>
@@ -25426,7 +25399,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
         <v>36</v>
       </c>
@@ -25434,7 +25407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="19" t="s">
         <v>24</v>
       </c>
@@ -25452,15 +25425,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE94ACBA-5F69-4911-8427-0D54C30D4C0E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A3:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>47</v>
       </c>
@@ -25474,7 +25447,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -25488,7 +25461,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -25502,7 +25475,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -25514,7 +25487,7 @@
       </c>
       <c r="D6" s="9"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>47</v>
       </c>
@@ -25522,7 +25495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -25530,7 +25503,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -25538,7 +25511,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>24</v>
       </c>
@@ -25556,15 +25529,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10730F53-1099-459F-BE17-73BB8AB9D61F}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A3:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>48</v>
       </c>
@@ -25578,7 +25551,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -25592,7 +25565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -25606,7 +25579,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -25620,7 +25593,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -25634,7 +25607,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
@@ -25646,7 +25619,7 @@
       </c>
       <c r="D8" s="9"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>48</v>
       </c>
@@ -25654,7 +25627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -25662,7 +25635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -25670,7 +25643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -25678,7 +25651,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -25686,7 +25659,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>24</v>
       </c>
@@ -25704,15 +25677,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADF40B5-799D-49EF-84DA-81B27C3CC8B3}">
   <sheetPr codeName="Planilha7"/>
   <dimension ref="A3:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
@@ -25726,7 +25699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -25740,7 +25713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -25754,7 +25727,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -25768,7 +25741,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -25780,7 +25753,7 @@
       </c>
       <c r="D7" s="9"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>6</v>
       </c>
@@ -25788,7 +25761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -25796,7 +25769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -25804,7 +25777,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -25812,7 +25785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>24</v>
       </c>
@@ -25830,15 +25803,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81FF32B4-D917-47CD-8634-6912E0CE5486}">
   <sheetPr codeName="Planilha8"/>
   <dimension ref="A3:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
@@ -25852,7 +25825,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -25866,7 +25839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -25880,7 +25853,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -25892,7 +25865,7 @@
       </c>
       <c r="D6" s="9"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -25900,7 +25873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -25908,7 +25881,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -25916,7 +25889,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>24</v>
       </c>

--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Exercicio de tudo até agora.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Exercicio de tudo até agora.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118F831C-1CED-460B-9244-1662C794FF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C4B6CE-3FFD-45AF-A619-1301F2363C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="647" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="58">
   <si>
     <t>ID</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>Variáveis</t>
+  </si>
+  <si>
+    <t>CV</t>
   </si>
 </sst>
 </file>
@@ -453,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -531,16 +534,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -552,13 +558,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -736,1809 +742,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Tempo Resposta</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Tempo Resposta'!$B$17</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Tempo Resposta'!$A$18:$A$26</c:f>
-              <c:strCache>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>115-144</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>145-174</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>175-204</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>205-234</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>235-264</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>265-294</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>295-324</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>325-354</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>385-414</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Tempo Resposta'!$B$18:$B$26</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0780-4050-B351-595E18FA9FE3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1747111791"/>
-        <c:axId val="1747118511"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1747111791"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1747118511"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1747118511"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1747111791"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Prioridade</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Prioridade!$B$10</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Prioridade!$A$11:$A$13</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Alta</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Baixa</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Média</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Prioridade!$B$11:$B$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1660-460F-B08C-098F2703508F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="1784088255"/>
-        <c:axId val="1784090175"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1784088255"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1784090175"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1784090175"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1784088255"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Prioridade</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Prioridade!$B$10</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Prioridade!$A$11:$A$13</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Alta</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Baixa</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Média</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Prioridade!$B$11:$B$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-742C-4513-AEC5-7F0739E6C391}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="1747648479"/>
-        <c:axId val="1747647519"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1747648479"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1747647519"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1747647519"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1747648479"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Status</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Status!$B$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-6444-47B5-A3C6-2919A4388BD1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-6444-47B5-A3C6-2919A4388BD1}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:cat>
-            <c:strRef>
-              <c:f>Status!$A$10:$A$11</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Erro</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Sucesso</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Status!$B$10:$B$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>42</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4804-403C-8CAD-1E748745BDAD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Status</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Status!$B$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Status!$A$10:$A$11</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Erro</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Sucesso</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Status!$B$10:$B$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>42</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2193-454E-9B86-153995FB4D39}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="1789424735"/>
-        <c:axId val="1789427135"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1789424735"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1789427135"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1789427135"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1789424735"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Status</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Status!$B$9</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Status!$A$10:$A$11</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Erro</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Sucesso</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Status!$B$10:$B$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>42</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-861A-4E29-908F-5156EED4F62A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="1775973215"/>
-        <c:axId val="1775969855"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1775973215"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1775969855"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1775969855"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1775973215"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -2949,7 +1152,1161 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Prioridade</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Prioridade!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prioridade!$A$11:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Alta</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Baixa</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Média</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prioridade!$B$11:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-742C-4513-AEC5-7F0739E6C391}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1747648479"/>
+        <c:axId val="1747647519"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1747648479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1747647519"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1747647519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1747648479"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Status</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Status!$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6444-47B5-A3C6-2919A4388BD1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6444-47B5-A3C6-2919A4388BD1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Status!$A$10:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Erro</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sucesso</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Status!$B$10:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4804-403C-8CAD-1E748745BDAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Status</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Status!$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Status!$A$10:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Erro</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sucesso</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Status!$B$10:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2193-454E-9B86-153995FB4D39}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1789424735"/>
+        <c:axId val="1789427135"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1789424735"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1789427135"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1789427135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1789424735"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Status</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Status!$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Status!$A$10:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Erro</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sucesso</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Status!$B$10:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-861A-4E29-908F-5156EED4F62A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1775973215"/>
+        <c:axId val="1775969855"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1775973215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1775969855"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1775969855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1775973215"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -3199,7 +2556,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -3499,7 +2856,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -3798,7 +3155,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -4100,7 +3457,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -4412,7 +3769,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -4723,7 +4080,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -4962,6 +4319,312 @@
         </a:p>
       </c:txPr>
     </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Prioridade</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Prioridade!$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Prioridade!$A$11:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Alta</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Baixa</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Média</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Prioridade!$B$11:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1660-460F-B08C-098F2703508F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1784088255"/>
+        <c:axId val="1784090175"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1784088255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1784090175"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1784090175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1784088255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -5575,46 +5238,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors17.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -6439,7 +6062,7 @@
 </file>
 
 <file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6643,22 +6266,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -6763,8 +6387,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -6896,19 +6520,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -6942,7 +6567,7 @@
 </file>
 
 <file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -6999,7 +6624,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -7050,6 +6675,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -7060,12 +6692,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -7103,7 +6742,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -7447,7 +7086,7 @@
 </file>
 
 <file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -7504,7 +7143,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -7555,13 +7194,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -7572,19 +7204,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -7622,7 +7247,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -7665,23 +7290,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -7786,8 +7410,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7919,20 +7543,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -7966,7 +7589,7 @@
 </file>
 
 <file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -8170,22 +7793,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -8290,8 +7914,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8423,19 +8047,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -8469,7 +8094,7 @@
 </file>
 
 <file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -8526,7 +8151,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -8577,6 +8202,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -8587,12 +8219,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -8630,7 +8269,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -8974,7 +8613,7 @@
 </file>
 
 <file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9031,7 +8670,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -9082,13 +8721,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -9099,19 +8731,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -9149,7 +8774,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -9192,23 +8817,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -9313,8 +8937,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9446,20 +9070,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -9493,7 +9116,7 @@
 </file>
 
 <file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9697,22 +9320,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -9817,8 +9441,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9950,19 +9574,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -9995,8 +9620,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10200,23 +9825,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -10321,8 +9945,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -10454,20 +10078,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -10500,8 +10123,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10528,8 +10151,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -10630,7 +10253,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -10662,10 +10285,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -10986,6 +10609,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -11005,7 +10639,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11508,8 +11142,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -11536,8 +11170,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -11566,7 +11200,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -11617,6 +11251,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -11627,18 +11268,25 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -11673,7 +11321,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -11994,17 +11642,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -12024,7 +11661,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -12527,8 +12164,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -12585,7 +12222,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -12636,13 +12273,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -12653,19 +12283,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -12703,7 +12326,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -13046,8 +12669,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -13104,7 +12727,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -13155,6 +12778,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -13165,12 +12795,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -13208,7 +12845,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -13251,22 +12888,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -13371,8 +13009,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -13504,19 +13142,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -13549,8 +13188,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -13754,23 +13393,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -13875,8 +13513,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -14008,539 +13646,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -15588,7 +14706,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> Não, a maioria dos resultados deram números próximos um dos outros.</a:t>
+            <a:t> Sim, pois a variação entre a variância e o desvio padrão é alto.</a:t>
           </a:r>
           <a:endParaRPr lang="pt-BR" sz="1200" b="0">
             <a:solidFill>
@@ -15699,42 +14817,6 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1019175</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>3175</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Gráfico 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EB3ED18-C93B-1EE6-114A-65D8A73A8152}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -22529,7 +21611,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:Y66"/>
+  <dimension ref="A1:Z66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
@@ -23851,7 +22933,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -23877,7 +22959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:26" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -23902,39 +22984,42 @@
       <c r="H50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J50" s="29" t="s">
+      <c r="J50" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="K50" s="30"/>
+      <c r="K50" s="38"/>
       <c r="L50" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N50" s="33" t="s">
+      <c r="N50" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="O50" s="33"/>
-      <c r="P50" s="33" t="s">
+      <c r="O50" s="34"/>
+      <c r="P50" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="Q50" s="33"/>
-      <c r="R50" s="33" t="s">
+      <c r="Q50" s="34"/>
+      <c r="R50" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="S50" s="33"/>
-      <c r="T50" s="33" t="s">
+      <c r="S50" s="34"/>
+      <c r="T50" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="U50" s="33"/>
-      <c r="V50" s="33" t="s">
+      <c r="U50" s="34"/>
+      <c r="V50" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="W50" s="33"/>
-      <c r="X50" s="33" t="s">
+      <c r="W50" s="34"/>
+      <c r="X50" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="Y50" s="33"/>
+      <c r="Y50" s="34"/>
+      <c r="Z50" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="51" spans="1:25" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:26" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -23959,44 +23044,48 @@
       <c r="H51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="31" t="s">
+      <c r="J51" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="K51" s="32"/>
+      <c r="K51" s="31"/>
       <c r="L51" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N51" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="N51" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="O51" s="33"/>
-      <c r="P51" s="33">
+      <c r="O51" s="34"/>
+      <c r="P51" s="34">
         <f>AVERAGE(B2:B61)</f>
         <v>207.8</v>
       </c>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="34" t="e" cm="1">
+      <c r="Q51" s="34"/>
+      <c r="R51" s="35" t="e" cm="1">
         <f t="array" ref="R51">_xlfn.MODE.MULT(B2:B61)</f>
         <v>#N/A</v>
       </c>
-      <c r="S51" s="35"/>
-      <c r="T51" s="33">
+      <c r="S51" s="36"/>
+      <c r="T51" s="34">
         <f>MEDIAN(B2:B61)</f>
         <v>189</v>
       </c>
-      <c r="U51" s="33"/>
-      <c r="V51" s="38">
+      <c r="U51" s="34"/>
+      <c r="V51" s="29">
         <f>_xlfn.VAR.S(B2:B61)</f>
         <v>4895.2135593220355</v>
       </c>
-      <c r="W51" s="38"/>
-      <c r="X51" s="38">
+      <c r="W51" s="29"/>
+      <c r="X51" s="29">
         <f>_xlfn.STDEV.S(B2:B61)</f>
         <v>69.965802784803628</v>
       </c>
-      <c r="Y51" s="38"/>
+      <c r="Y51" s="29"/>
+      <c r="Z51" s="39">
+        <f>X51/P51*100</f>
+        <v>33.669779973437741</v>
+      </c>
     </row>
-    <row r="52" spans="1:25" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:26" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -24021,44 +23110,48 @@
       <c r="H52" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J52" s="31" t="s">
+      <c r="J52" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="K52" s="32"/>
+      <c r="K52" s="31"/>
       <c r="L52" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N52" s="33" t="s">
+      <c r="N52" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="O52" s="33"/>
-      <c r="P52" s="38">
+      <c r="O52" s="34"/>
+      <c r="P52" s="29">
         <f>AVERAGE(C2:C61)</f>
         <v>8.4833333333333325</v>
       </c>
-      <c r="Q52" s="38"/>
-      <c r="R52" s="33" cm="1">
+      <c r="Q52" s="29"/>
+      <c r="R52" s="34" cm="1">
         <f t="array" ref="R52">_xlfn.MODE.MULT(C2:C61)</f>
         <v>7</v>
       </c>
-      <c r="S52" s="33"/>
-      <c r="T52" s="33">
+      <c r="S52" s="34"/>
+      <c r="T52" s="34">
         <f>MEDIAN(C2:C61)</f>
         <v>8</v>
       </c>
-      <c r="U52" s="33"/>
-      <c r="V52" s="38">
+      <c r="U52" s="34"/>
+      <c r="V52" s="29">
         <f>_xlfn.VAR.S(C2:C61)</f>
         <v>17.135310734463282</v>
       </c>
-      <c r="W52" s="38"/>
-      <c r="X52" s="38">
+      <c r="W52" s="29"/>
+      <c r="X52" s="29">
         <f>_xlfn.STDEV.S(C2:C61)</f>
         <v>4.1394819403475216</v>
       </c>
-      <c r="Y52" s="38"/>
+      <c r="Y52" s="29"/>
+      <c r="Z52" s="39">
+        <f>X52/P52*100</f>
+        <v>48.79546491568788</v>
+      </c>
     </row>
-    <row r="53" spans="1:25" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:26" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -24083,44 +23176,48 @@
       <c r="H53" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J53" s="31" t="s">
+      <c r="J53" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="K53" s="32"/>
+      <c r="K53" s="31"/>
       <c r="L53" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N53" s="33" t="s">
+      <c r="N53" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="O53" s="33"/>
-      <c r="P53" s="38">
+      <c r="O53" s="34"/>
+      <c r="P53" s="29">
         <f>AVERAGE(D2:D61)</f>
         <v>2.9283333333333332</v>
       </c>
-      <c r="Q53" s="38"/>
+      <c r="Q53" s="29"/>
       <c r="R53" s="27" cm="1">
         <f t="array" ref="R53:R66">_xlfn.MODE.MULT(D2:D61)</f>
         <v>1.2</v>
       </c>
       <c r="S53" s="28"/>
-      <c r="T53" s="33">
+      <c r="T53" s="34">
         <f>MEDIAN(D2:D61)</f>
         <v>2.5</v>
       </c>
-      <c r="U53" s="33"/>
-      <c r="V53" s="38">
+      <c r="U53" s="34"/>
+      <c r="V53" s="29">
         <f>_xlfn.VAR.S(D2:D61)</f>
         <v>3.4322344632768327</v>
       </c>
-      <c r="W53" s="38"/>
-      <c r="X53" s="38">
+      <c r="W53" s="29"/>
+      <c r="X53" s="29">
         <f>_xlfn.STDEV.S(D2:D61)</f>
         <v>1.8526290679131732</v>
       </c>
-      <c r="Y53" s="38"/>
+      <c r="Y53" s="29"/>
+      <c r="Z53" s="39">
+        <f>X53/P53*100</f>
+        <v>63.26564830665361</v>
+      </c>
     </row>
-    <row r="54" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -24145,10 +23242,10 @@
       <c r="H54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J54" s="31" t="s">
+      <c r="J54" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="32"/>
+      <c r="K54" s="31"/>
       <c r="L54" s="6" t="s">
         <v>19</v>
       </c>
@@ -24156,7 +23253,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -24181,10 +23278,10 @@
       <c r="H55" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J55" s="31" t="s">
+      <c r="J55" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="K55" s="32"/>
+      <c r="K55" s="31"/>
       <c r="L55" s="6" t="s">
         <v>19</v>
       </c>
@@ -24192,7 +23289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -24217,10 +23314,10 @@
       <c r="H56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J56" s="31" t="s">
+      <c r="J56" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="K56" s="32"/>
+      <c r="K56" s="31"/>
       <c r="L56" s="6" t="s">
         <v>20</v>
       </c>
@@ -24228,7 +23325,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -24253,10 +23350,10 @@
       <c r="H57" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J57" s="36" t="s">
+      <c r="J57" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="K57" s="37"/>
+      <c r="K57" s="33"/>
       <c r="L57" s="7" t="s">
         <v>19</v>
       </c>
@@ -24264,7 +23361,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -24293,7 +23390,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -24322,7 +23419,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -24351,7 +23448,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -24380,17 +23477,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
       <c r="R62">
         <v>0.9</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
       <c r="R63">
         <v>0.7</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
       <c r="R64">
         <v>0.6</v>
       </c>
@@ -24407,11 +23504,12 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="X51:Y51"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="J53:K53"/>
     <mergeCell ref="N50:O50"/>
     <mergeCell ref="X53:Y53"/>
     <mergeCell ref="T53:U53"/>
@@ -24428,16 +23526,15 @@
     <mergeCell ref="R50:S50"/>
     <mergeCell ref="T50:U50"/>
     <mergeCell ref="T51:U51"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="X51:Y51"/>
     <mergeCell ref="T52:U52"/>
     <mergeCell ref="R51:S51"/>
     <mergeCell ref="R52:S52"/>
     <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="J53:K53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Exercicio de tudo até agora.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Exercicio de tudo até agora.xlsx
@@ -2,25 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="EstaPastaDeTrabalho" hidePivotFieldList="1"/>
+  <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C4B6CE-3FFD-45AF-A619-1301F2363C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0D932E-EDDB-4D39-9E85-8E4BD7CFCB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="647" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="647" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados_TI" sheetId="1" r:id="rId1"/>
-    <sheet name="Tempo Resposta" sheetId="2" r:id="rId2"/>
-    <sheet name="Sessão" sheetId="3" r:id="rId3"/>
-    <sheet name="Tamanho Mb" sheetId="4" r:id="rId4"/>
-    <sheet name="Usuário" sheetId="5" r:id="rId5"/>
-    <sheet name="Região" sheetId="6" r:id="rId6"/>
-    <sheet name="Prioridade" sheetId="7" r:id="rId7"/>
-    <sheet name="Status" sheetId="8" r:id="rId8"/>
+    <sheet name="Planilha1" sheetId="9" r:id="rId1"/>
+    <sheet name="Dados_TI" sheetId="1" r:id="rId2"/>
+    <sheet name="Tempo Resposta" sheetId="2" r:id="rId3"/>
+    <sheet name="Sessão" sheetId="3" r:id="rId4"/>
+    <sheet name="Tamanho Mb" sheetId="4" r:id="rId5"/>
+    <sheet name="Usuário" sheetId="5" r:id="rId6"/>
+    <sheet name="Região" sheetId="6" r:id="rId7"/>
+    <sheet name="Prioridade" sheetId="7" r:id="rId8"/>
+    <sheet name="Status" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">'Tempo Resposta'!$A$18:$A$26</definedName>
@@ -35,13 +36,18 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
-    <pivotCache cacheId="1" r:id="rId10"/>
-    <pivotCache cacheId="2" r:id="rId11"/>
-    <pivotCache cacheId="3" r:id="rId12"/>
-    <pivotCache cacheId="4" r:id="rId13"/>
-    <pivotCache cacheId="5" r:id="rId14"/>
-    <pivotCache cacheId="6" r:id="rId15"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
+    <pivotCache cacheId="1" r:id="rId11"/>
+    <pivotCache cacheId="2" r:id="rId12"/>
+    <pivotCache cacheId="3" r:id="rId13"/>
+    <pivotCache cacheId="4" r:id="rId14"/>
+    <pivotCache cacheId="5" r:id="rId15"/>
+    <pivotCache cacheId="6" r:id="rId16"/>
+    <pivotCache cacheId="13" r:id="rId17"/>
+    <pivotCache cacheId="23" r:id="rId18"/>
+    <pivotCache cacheId="29" r:id="rId19"/>
+    <pivotCache cacheId="36" r:id="rId20"/>
+    <pivotCache cacheId="44" r:id="rId21"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -85,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -259,6 +265,33 @@
   </si>
   <si>
     <t>CV</t>
+  </si>
+  <si>
+    <t>Rótulos de Coluna</t>
+  </si>
+  <si>
+    <t>Contagem de Regiao</t>
+  </si>
+  <si>
+    <t>Regiões</t>
+  </si>
+  <si>
+    <t>Contagem de Tipo_Usuario</t>
+  </si>
+  <si>
+    <t>Tipos de usuario</t>
+  </si>
+  <si>
+    <t>Média de Tempo_Resposta_ms</t>
+  </si>
+  <si>
+    <t>Contagem de Status</t>
+  </si>
+  <si>
+    <t>Prioridades</t>
+  </si>
+  <si>
+    <t>Tipos de Usuários</t>
   </si>
 </sst>
 </file>
@@ -456,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -534,7 +567,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -543,13 +582,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -558,20 +600,214 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="117">
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -13696,15 +13932,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>14109</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>85724</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>44802</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>162278</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -13719,8 +13955,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7210425" y="0"/>
-          <a:ext cx="10858500" cy="7515224"/>
+          <a:off x="6921853" y="12191998"/>
+          <a:ext cx="11037005" cy="10604502"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14732,6 +14968,263 @@
             <a:t> </a:t>
           </a:r>
         </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>6) Análises com Variáveis Qualitativas</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>a)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> Qual região apresenta mais erros?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: A região que apresenta mais erros é a região Norte.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>b) Usuários internos ou externos têm maior tempo médio?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: Os usuários externos possuem maior tempo médio.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>c) Qual o tempo médio por região?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: Nordeste - 202; Norte - 220; Sudeste - 215; Sul - 196.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>d) Qual o tempo médio por tipo de usuário?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: Externo - 210; Interno - 206.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>e) Qual a taxa de erro por prioridade?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>R: Alta - 25%   Média -  33,33%   Baixa - 41,67%</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>OBS: Use cruzamentos de variáveis para responder (tabela dinâmica)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1200" b="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
@@ -15723,6 +16216,148 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aluno" refreshedDate="46120.429916435183" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{A0B6937C-5A89-4365-875A-B5F8FEC09E80}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:H61" sheet="Dados_TI"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="60"/>
+    </cacheField>
+    <cacheField name="Tempo_Resposta_ms" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="115" maxValue="400"/>
+    </cacheField>
+    <cacheField name="Requisicoes_por_Sessao" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="18"/>
+    </cacheField>
+    <cacheField name="Tamanho_MB" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="7"/>
+    </cacheField>
+    <cacheField name="Tipo_Usuario" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Regiao" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Sudeste"/>
+        <s v="Sul"/>
+        <s v="Nordeste"/>
+        <s v="Norte"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Prioridade" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aluno" refreshedDate="46120.435422106479" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{63E70A75-0F75-4387-BB59-F5D198E533F3}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:H61" sheet="Dados_TI"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="60"/>
+    </cacheField>
+    <cacheField name="Tempo_Resposta_ms" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="115" maxValue="400"/>
+    </cacheField>
+    <cacheField name="Requisicoes_por_Sessao" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="18"/>
+    </cacheField>
+    <cacheField name="Tamanho_MB" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="7"/>
+    </cacheField>
+    <cacheField name="Tipo_Usuario" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Externo"/>
+        <s v="Interno"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Regiao" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Sudeste"/>
+        <s v="Sul"/>
+        <s v="Nordeste"/>
+        <s v="Norte"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Prioridade" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aluno" refreshedDate="46120.437043518519" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{43F2F1CC-262D-41F9-A0BF-5D6A3CC1F38B}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:H61" sheet="Dados_TI"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="60"/>
+    </cacheField>
+    <cacheField name="Tempo_Resposta_ms" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="115" maxValue="400"/>
+    </cacheField>
+    <cacheField name="Requisicoes_por_Sessao" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="18"/>
+    </cacheField>
+    <cacheField name="Tamanho_MB" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="7"/>
+    </cacheField>
+    <cacheField name="Tipo_Usuario" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Regiao" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Sudeste"/>
+        <s v="Sul"/>
+        <s v="Nordeste"/>
+        <s v="Norte"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Prioridade" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Baixa"/>
+        <s v="Média"/>
+        <s v="Alta"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Sucesso"/>
+        <s v="Erro"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aluno" refreshedDate="46112.470983449071" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{647D5437-E62F-41A5-B56C-31CDF4901208}">
   <cacheSource type="worksheet">
@@ -16075,6 +16710,161 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aluno" refreshedDate="46120.423547569444" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{25E00552-98DC-467F-A1C6-2B915542A534}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:H61" sheet="Dados_TI"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="60"/>
+    </cacheField>
+    <cacheField name="Tempo_Resposta_ms" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="115" maxValue="400"/>
+    </cacheField>
+    <cacheField name="Requisicoes_por_Sessao" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="18"/>
+    </cacheField>
+    <cacheField name="Tamanho_MB" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="7"/>
+    </cacheField>
+    <cacheField name="Tipo_Usuario" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Regiao" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Sudeste"/>
+        <s v="Sul"/>
+        <s v="Nordeste"/>
+        <s v="Norte"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Prioridade" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Sucesso"/>
+        <s v="Erro"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aluno" refreshedDate="46120.427628124999" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{0CD465FA-6D90-458D-B89C-CB17D3B40459}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:H61" sheet="Dados_TI"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="60"/>
+    </cacheField>
+    <cacheField name="Tempo_Resposta_ms" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="115" maxValue="400" count="60">
+        <n v="120"/>
+        <n v="135"/>
+        <n v="150"/>
+        <n v="160"/>
+        <n v="145"/>
+        <n v="155"/>
+        <n v="170"/>
+        <n v="180"/>
+        <n v="175"/>
+        <n v="165"/>
+        <n v="140"/>
+        <n v="130"/>
+        <n v="125"/>
+        <n v="200"/>
+        <n v="210"/>
+        <n v="190"/>
+        <n v="185"/>
+        <n v="220"/>
+        <n v="230"/>
+        <n v="240"/>
+        <n v="250"/>
+        <n v="260"/>
+        <n v="270"/>
+        <n v="300"/>
+        <n v="310"/>
+        <n v="320"/>
+        <n v="330"/>
+        <n v="340"/>
+        <n v="350"/>
+        <n v="400"/>
+        <n v="115"/>
+        <n v="118"/>
+        <n v="122"/>
+        <n v="128"/>
+        <n v="132"/>
+        <n v="138"/>
+        <n v="142"/>
+        <n v="148"/>
+        <n v="152"/>
+        <n v="158"/>
+        <n v="162"/>
+        <n v="168"/>
+        <n v="172"/>
+        <n v="178"/>
+        <n v="182"/>
+        <n v="188"/>
+        <n v="192"/>
+        <n v="198"/>
+        <n v="205"/>
+        <n v="215"/>
+        <n v="225"/>
+        <n v="235"/>
+        <n v="245"/>
+        <n v="255"/>
+        <n v="265"/>
+        <n v="275"/>
+        <n v="285"/>
+        <n v="295"/>
+        <n v="305"/>
+        <n v="315"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Requisicoes_por_Sessao" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="18"/>
+    </cacheField>
+    <cacheField name="Tamanho_MB" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.5" maxValue="7"/>
+    </cacheField>
+    <cacheField name="Tipo_Usuario" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Externo"/>
+        <s v="Interno"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Regiao" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Sudeste"/>
+        <s v="Sul"/>
+        <s v="Nordeste"/>
+        <s v="Norte"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Prioridade" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Status" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
   <r>
@@ -16680,6 +17470,1821 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <n v="1"/>
+    <n v="120"/>
+    <n v="5"/>
+    <n v="1.2"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <n v="135"/>
+    <n v="3"/>
+    <n v="0.8"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <n v="150"/>
+    <n v="6"/>
+    <n v="1.5"/>
+    <s v="Interno"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <n v="160"/>
+    <n v="4"/>
+    <n v="2"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <n v="145"/>
+    <n v="7"/>
+    <n v="1.1000000000000001"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <n v="155"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <n v="170"/>
+    <n v="8"/>
+    <n v="2.5"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <n v="180"/>
+    <n v="6"/>
+    <n v="2.2000000000000002"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <n v="175"/>
+    <n v="7"/>
+    <n v="1.8"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <n v="165"/>
+    <n v="4"/>
+    <n v="1"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Alta"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="140"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <n v="130"/>
+    <n v="2"/>
+    <n v="0.7"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <n v="125"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <n v="200"/>
+    <n v="9"/>
+    <n v="3"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <n v="210"/>
+    <n v="10"/>
+    <n v="3.2"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <n v="190"/>
+    <n v="8"/>
+    <n v="2.8"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <n v="185"/>
+    <n v="7"/>
+    <n v="2.4"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <n v="220"/>
+    <n v="11"/>
+    <n v="3.5"/>
+    <s v="Externo"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <n v="230"/>
+    <n v="12"/>
+    <n v="3.8"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <n v="240"/>
+    <n v="10"/>
+    <n v="4"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <n v="250"/>
+    <n v="9"/>
+    <n v="4.2"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <n v="260"/>
+    <n v="11"/>
+    <n v="4.5"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <n v="270"/>
+    <n v="12"/>
+    <n v="4.8"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <n v="300"/>
+    <n v="13"/>
+    <n v="5"/>
+    <s v="Externo"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <n v="310"/>
+    <n v="14"/>
+    <n v="5.5"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <n v="320"/>
+    <n v="13"/>
+    <n v="5.8"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <n v="330"/>
+    <n v="15"/>
+    <n v="6"/>
+    <s v="Interno"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <n v="340"/>
+    <n v="14"/>
+    <n v="6.2"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <n v="350"/>
+    <n v="16"/>
+    <n v="6.5"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <n v="400"/>
+    <n v="18"/>
+    <n v="7"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <n v="115"/>
+    <n v="2"/>
+    <n v="0.5"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <n v="118"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <n v="122"/>
+    <n v="4"/>
+    <n v="0.7"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <n v="128"/>
+    <n v="2"/>
+    <n v="0.8"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <n v="132"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <n v="138"/>
+    <n v="4"/>
+    <n v="1"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <n v="142"/>
+    <n v="5"/>
+    <n v="1.1000000000000001"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <n v="148"/>
+    <n v="6"/>
+    <n v="1.2"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <n v="152"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <n v="158"/>
+    <n v="4"/>
+    <n v="1.4"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <n v="162"/>
+    <n v="6"/>
+    <n v="1.6"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <n v="168"/>
+    <n v="7"/>
+    <n v="1.7"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <n v="172"/>
+    <n v="8"/>
+    <n v="1.8"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <n v="178"/>
+    <n v="7"/>
+    <n v="1.9"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <n v="182"/>
+    <n v="6"/>
+    <n v="2"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <n v="188"/>
+    <n v="8"/>
+    <n v="2.2000000000000002"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <n v="192"/>
+    <n v="9"/>
+    <n v="2.5"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <n v="198"/>
+    <n v="7"/>
+    <n v="2.7"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <n v="205"/>
+    <n v="10"/>
+    <n v="3"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <n v="215"/>
+    <n v="11"/>
+    <n v="3.3"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <n v="225"/>
+    <n v="12"/>
+    <n v="3.6"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <n v="235"/>
+    <n v="13"/>
+    <n v="3.9"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="53"/>
+    <n v="245"/>
+    <n v="11"/>
+    <n v="4.0999999999999996"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="54"/>
+    <n v="255"/>
+    <n v="10"/>
+    <n v="4.3"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="55"/>
+    <n v="265"/>
+    <n v="12"/>
+    <n v="4.5999999999999996"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="56"/>
+    <n v="275"/>
+    <n v="13"/>
+    <n v="4.9000000000000004"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="57"/>
+    <n v="285"/>
+    <n v="14"/>
+    <n v="5.2"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <n v="295"/>
+    <n v="13"/>
+    <n v="5.4"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="59"/>
+    <n v="305"/>
+    <n v="15"/>
+    <n v="5.7"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <n v="315"/>
+    <n v="14"/>
+    <n v="6"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <n v="1"/>
+    <n v="120"/>
+    <n v="5"/>
+    <n v="1.2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <n v="135"/>
+    <n v="3"/>
+    <n v="0.8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <n v="150"/>
+    <n v="6"/>
+    <n v="1.5"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <n v="160"/>
+    <n v="4"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <n v="145"/>
+    <n v="7"/>
+    <n v="1.1000000000000001"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <n v="155"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <n v="170"/>
+    <n v="8"/>
+    <n v="2.5"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <n v="180"/>
+    <n v="6"/>
+    <n v="2.2000000000000002"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <n v="175"/>
+    <n v="7"/>
+    <n v="1.8"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <n v="165"/>
+    <n v="4"/>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Alta"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="140"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <n v="130"/>
+    <n v="2"/>
+    <n v="0.7"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <n v="125"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <n v="200"/>
+    <n v="9"/>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <n v="210"/>
+    <n v="10"/>
+    <n v="3.2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <n v="190"/>
+    <n v="8"/>
+    <n v="2.8"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <n v="185"/>
+    <n v="7"/>
+    <n v="2.4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <n v="220"/>
+    <n v="11"/>
+    <n v="3.5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <n v="230"/>
+    <n v="12"/>
+    <n v="3.8"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <n v="240"/>
+    <n v="10"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <n v="250"/>
+    <n v="9"/>
+    <n v="4.2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <n v="260"/>
+    <n v="11"/>
+    <n v="4.5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <n v="270"/>
+    <n v="12"/>
+    <n v="4.8"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <n v="300"/>
+    <n v="13"/>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <n v="310"/>
+    <n v="14"/>
+    <n v="5.5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <n v="320"/>
+    <n v="13"/>
+    <n v="5.8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <n v="330"/>
+    <n v="15"/>
+    <n v="6"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <n v="340"/>
+    <n v="14"/>
+    <n v="6.2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <n v="350"/>
+    <n v="16"/>
+    <n v="6.5"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <n v="400"/>
+    <n v="18"/>
+    <n v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <n v="115"/>
+    <n v="2"/>
+    <n v="0.5"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <n v="118"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <n v="122"/>
+    <n v="4"/>
+    <n v="0.7"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <n v="128"/>
+    <n v="2"/>
+    <n v="0.8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <n v="132"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <n v="138"/>
+    <n v="4"/>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <n v="142"/>
+    <n v="5"/>
+    <n v="1.1000000000000001"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <n v="148"/>
+    <n v="6"/>
+    <n v="1.2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <n v="152"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <n v="158"/>
+    <n v="4"/>
+    <n v="1.4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <n v="162"/>
+    <n v="6"/>
+    <n v="1.6"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <n v="168"/>
+    <n v="7"/>
+    <n v="1.7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <n v="172"/>
+    <n v="8"/>
+    <n v="1.8"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <n v="178"/>
+    <n v="7"/>
+    <n v="1.9"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <n v="182"/>
+    <n v="6"/>
+    <n v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <n v="188"/>
+    <n v="8"/>
+    <n v="2.2000000000000002"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <n v="192"/>
+    <n v="9"/>
+    <n v="2.5"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <n v="198"/>
+    <n v="7"/>
+    <n v="2.7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <n v="205"/>
+    <n v="10"/>
+    <n v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <n v="215"/>
+    <n v="11"/>
+    <n v="3.3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <n v="225"/>
+    <n v="12"/>
+    <n v="3.6"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <n v="235"/>
+    <n v="13"/>
+    <n v="3.9"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="53"/>
+    <n v="245"/>
+    <n v="11"/>
+    <n v="4.0999999999999996"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="54"/>
+    <n v="255"/>
+    <n v="10"/>
+    <n v="4.3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="55"/>
+    <n v="265"/>
+    <n v="12"/>
+    <n v="4.5999999999999996"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="56"/>
+    <n v="275"/>
+    <n v="13"/>
+    <n v="4.9000000000000004"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="57"/>
+    <n v="285"/>
+    <n v="14"/>
+    <n v="5.2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <n v="295"/>
+    <n v="13"/>
+    <n v="5.4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="59"/>
+    <n v="305"/>
+    <n v="15"/>
+    <n v="5.7"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <n v="315"/>
+    <n v="14"/>
+    <n v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <n v="1"/>
+    <n v="120"/>
+    <n v="5"/>
+    <n v="1.2"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <n v="135"/>
+    <n v="3"/>
+    <n v="0.8"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <n v="150"/>
+    <n v="6"/>
+    <n v="1.5"/>
+    <s v="Interno"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <n v="160"/>
+    <n v="4"/>
+    <n v="2"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <n v="145"/>
+    <n v="7"/>
+    <n v="1.1000000000000001"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <n v="155"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <n v="170"/>
+    <n v="8"/>
+    <n v="2.5"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <n v="180"/>
+    <n v="6"/>
+    <n v="2.2000000000000002"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <n v="175"/>
+    <n v="7"/>
+    <n v="1.8"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <n v="165"/>
+    <n v="4"/>
+    <n v="1"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="140"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <n v="130"/>
+    <n v="2"/>
+    <n v="0.7"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <n v="125"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <n v="200"/>
+    <n v="9"/>
+    <n v="3"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <n v="210"/>
+    <n v="10"/>
+    <n v="3.2"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <n v="190"/>
+    <n v="8"/>
+    <n v="2.8"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <n v="185"/>
+    <n v="7"/>
+    <n v="2.4"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <n v="220"/>
+    <n v="11"/>
+    <n v="3.5"/>
+    <s v="Externo"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <n v="230"/>
+    <n v="12"/>
+    <n v="3.8"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <n v="240"/>
+    <n v="10"/>
+    <n v="4"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <n v="250"/>
+    <n v="9"/>
+    <n v="4.2"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <n v="260"/>
+    <n v="11"/>
+    <n v="4.5"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <n v="270"/>
+    <n v="12"/>
+    <n v="4.8"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <n v="300"/>
+    <n v="13"/>
+    <n v="5"/>
+    <s v="Externo"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <n v="310"/>
+    <n v="14"/>
+    <n v="5.5"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <n v="320"/>
+    <n v="13"/>
+    <n v="5.8"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <n v="330"/>
+    <n v="15"/>
+    <n v="6"/>
+    <s v="Interno"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <n v="340"/>
+    <n v="14"/>
+    <n v="6.2"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <n v="350"/>
+    <n v="16"/>
+    <n v="6.5"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <n v="400"/>
+    <n v="18"/>
+    <n v="7"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <n v="115"/>
+    <n v="2"/>
+    <n v="0.5"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <n v="118"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <n v="122"/>
+    <n v="4"/>
+    <n v="0.7"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <n v="128"/>
+    <n v="2"/>
+    <n v="0.8"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <n v="132"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <n v="138"/>
+    <n v="4"/>
+    <n v="1"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <n v="142"/>
+    <n v="5"/>
+    <n v="1.1000000000000001"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <n v="148"/>
+    <n v="6"/>
+    <n v="1.2"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <n v="152"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <n v="158"/>
+    <n v="4"/>
+    <n v="1.4"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <n v="162"/>
+    <n v="6"/>
+    <n v="1.6"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <n v="168"/>
+    <n v="7"/>
+    <n v="1.7"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <n v="172"/>
+    <n v="8"/>
+    <n v="1.8"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <n v="178"/>
+    <n v="7"/>
+    <n v="1.9"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <n v="182"/>
+    <n v="6"/>
+    <n v="2"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <n v="188"/>
+    <n v="8"/>
+    <n v="2.2000000000000002"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <n v="192"/>
+    <n v="9"/>
+    <n v="2.5"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <n v="198"/>
+    <n v="7"/>
+    <n v="2.7"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <n v="205"/>
+    <n v="10"/>
+    <n v="3"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <n v="215"/>
+    <n v="11"/>
+    <n v="3.3"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <n v="225"/>
+    <n v="12"/>
+    <n v="3.6"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <n v="235"/>
+    <n v="13"/>
+    <n v="3.9"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="53"/>
+    <n v="245"/>
+    <n v="11"/>
+    <n v="4.0999999999999996"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="54"/>
+    <n v="255"/>
+    <n v="10"/>
+    <n v="4.3"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="55"/>
+    <n v="265"/>
+    <n v="12"/>
+    <n v="4.5999999999999996"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="56"/>
+    <n v="275"/>
+    <n v="13"/>
+    <n v="4.9000000000000004"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="57"/>
+    <n v="285"/>
+    <n v="14"/>
+    <n v="5.2"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <n v="295"/>
+    <n v="13"/>
+    <n v="5.4"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="59"/>
+    <n v="305"/>
+    <n v="15"/>
+    <n v="5.7"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <n v="315"/>
+    <n v="14"/>
+    <n v="6"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
   <r>
@@ -20310,7 +22915,2109 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <n v="1"/>
+    <n v="120"/>
+    <n v="5"/>
+    <n v="1.2"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <n v="135"/>
+    <n v="3"/>
+    <n v="0.8"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <n v="150"/>
+    <n v="6"/>
+    <n v="1.5"/>
+    <s v="Interno"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <n v="160"/>
+    <n v="4"/>
+    <n v="2"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <n v="145"/>
+    <n v="7"/>
+    <n v="1.1000000000000001"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <n v="155"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <n v="170"/>
+    <n v="8"/>
+    <n v="2.5"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <n v="180"/>
+    <n v="6"/>
+    <n v="2.2000000000000002"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <n v="175"/>
+    <n v="7"/>
+    <n v="1.8"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <n v="165"/>
+    <n v="4"/>
+    <n v="1"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Alta"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="140"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <n v="130"/>
+    <n v="2"/>
+    <n v="0.7"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <n v="125"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <n v="200"/>
+    <n v="9"/>
+    <n v="3"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <n v="210"/>
+    <n v="10"/>
+    <n v="3.2"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <n v="190"/>
+    <n v="8"/>
+    <n v="2.8"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <n v="185"/>
+    <n v="7"/>
+    <n v="2.4"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <n v="220"/>
+    <n v="11"/>
+    <n v="3.5"/>
+    <s v="Externo"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <n v="230"/>
+    <n v="12"/>
+    <n v="3.8"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <n v="240"/>
+    <n v="10"/>
+    <n v="4"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <n v="250"/>
+    <n v="9"/>
+    <n v="4.2"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <n v="260"/>
+    <n v="11"/>
+    <n v="4.5"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <n v="270"/>
+    <n v="12"/>
+    <n v="4.8"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <n v="300"/>
+    <n v="13"/>
+    <n v="5"/>
+    <s v="Externo"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <n v="310"/>
+    <n v="14"/>
+    <n v="5.5"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <n v="320"/>
+    <n v="13"/>
+    <n v="5.8"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <n v="330"/>
+    <n v="15"/>
+    <n v="6"/>
+    <s v="Interno"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <n v="340"/>
+    <n v="14"/>
+    <n v="6.2"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <n v="350"/>
+    <n v="16"/>
+    <n v="6.5"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <n v="400"/>
+    <n v="18"/>
+    <n v="7"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <n v="115"/>
+    <n v="2"/>
+    <n v="0.5"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <n v="118"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <n v="122"/>
+    <n v="4"/>
+    <n v="0.7"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <n v="128"/>
+    <n v="2"/>
+    <n v="0.8"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <n v="132"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <n v="138"/>
+    <n v="4"/>
+    <n v="1"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <n v="142"/>
+    <n v="5"/>
+    <n v="1.1000000000000001"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <n v="148"/>
+    <n v="6"/>
+    <n v="1.2"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <n v="152"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <n v="158"/>
+    <n v="4"/>
+    <n v="1.4"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <n v="162"/>
+    <n v="6"/>
+    <n v="1.6"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <n v="168"/>
+    <n v="7"/>
+    <n v="1.7"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <n v="172"/>
+    <n v="8"/>
+    <n v="1.8"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <n v="178"/>
+    <n v="7"/>
+    <n v="1.9"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <n v="182"/>
+    <n v="6"/>
+    <n v="2"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <n v="188"/>
+    <n v="8"/>
+    <n v="2.2000000000000002"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <n v="192"/>
+    <n v="9"/>
+    <n v="2.5"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <n v="198"/>
+    <n v="7"/>
+    <n v="2.7"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <n v="205"/>
+    <n v="10"/>
+    <n v="3"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <n v="215"/>
+    <n v="11"/>
+    <n v="3.3"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <n v="225"/>
+    <n v="12"/>
+    <n v="3.6"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <n v="235"/>
+    <n v="13"/>
+    <n v="3.9"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="53"/>
+    <n v="245"/>
+    <n v="11"/>
+    <n v="4.0999999999999996"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="54"/>
+    <n v="255"/>
+    <n v="10"/>
+    <n v="4.3"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="55"/>
+    <n v="265"/>
+    <n v="12"/>
+    <n v="4.5999999999999996"/>
+    <s v="Interno"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="56"/>
+    <n v="275"/>
+    <n v="13"/>
+    <n v="4.9000000000000004"/>
+    <s v="Externo"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="57"/>
+    <n v="285"/>
+    <n v="14"/>
+    <n v="5.2"/>
+    <s v="Interno"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <n v="295"/>
+    <n v="13"/>
+    <n v="5.4"/>
+    <s v="Externo"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="59"/>
+    <n v="305"/>
+    <n v="15"/>
+    <n v="5.7"/>
+    <s v="Interno"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <n v="315"/>
+    <n v="14"/>
+    <n v="6"/>
+    <s v="Externo"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="1.2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="0.8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <n v="6"/>
+    <n v="1.5"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <n v="4"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <n v="7"/>
+    <n v="1.1000000000000001"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <n v="8"/>
+    <n v="2.5"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <n v="6"/>
+    <n v="2.2000000000000002"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="7"/>
+    <n v="1.8"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <n v="4"/>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Alta"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <x v="10"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <x v="11"/>
+    <n v="2"/>
+    <n v="0.7"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <x v="12"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <x v="13"/>
+    <n v="9"/>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <x v="14"/>
+    <n v="10"/>
+    <n v="3.2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <x v="15"/>
+    <n v="8"/>
+    <n v="2.8"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <x v="16"/>
+    <n v="7"/>
+    <n v="2.4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <x v="17"/>
+    <n v="11"/>
+    <n v="3.5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <x v="18"/>
+    <n v="12"/>
+    <n v="3.8"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <x v="19"/>
+    <n v="10"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <x v="20"/>
+    <n v="9"/>
+    <n v="4.2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <x v="21"/>
+    <n v="11"/>
+    <n v="4.5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <x v="22"/>
+    <n v="12"/>
+    <n v="4.8"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <x v="23"/>
+    <n v="13"/>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <x v="24"/>
+    <n v="14"/>
+    <n v="5.5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <x v="25"/>
+    <n v="13"/>
+    <n v="5.8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <x v="26"/>
+    <n v="15"/>
+    <n v="6"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <x v="27"/>
+    <n v="14"/>
+    <n v="6.2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <x v="28"/>
+    <n v="16"/>
+    <n v="6.5"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <x v="29"/>
+    <n v="18"/>
+    <n v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <x v="30"/>
+    <n v="2"/>
+    <n v="0.5"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <x v="31"/>
+    <n v="3"/>
+    <n v="0.6"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <x v="32"/>
+    <n v="4"/>
+    <n v="0.7"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <x v="33"/>
+    <n v="2"/>
+    <n v="0.8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <x v="34"/>
+    <n v="3"/>
+    <n v="0.9"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <x v="35"/>
+    <n v="4"/>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <x v="36"/>
+    <n v="5"/>
+    <n v="1.1000000000000001"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <x v="37"/>
+    <n v="6"/>
+    <n v="1.2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <x v="38"/>
+    <n v="5"/>
+    <n v="1.3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <x v="39"/>
+    <n v="4"/>
+    <n v="1.4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <x v="40"/>
+    <n v="6"/>
+    <n v="1.6"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <x v="41"/>
+    <n v="7"/>
+    <n v="1.7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <x v="42"/>
+    <n v="8"/>
+    <n v="1.8"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <x v="43"/>
+    <n v="7"/>
+    <n v="1.9"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <x v="44"/>
+    <n v="6"/>
+    <n v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <x v="45"/>
+    <n v="8"/>
+    <n v="2.2000000000000002"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <x v="46"/>
+    <n v="9"/>
+    <n v="2.5"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <x v="47"/>
+    <n v="7"/>
+    <n v="2.7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <x v="48"/>
+    <n v="10"/>
+    <n v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <x v="49"/>
+    <n v="11"/>
+    <n v="3.3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="51"/>
+    <x v="50"/>
+    <n v="12"/>
+    <n v="3.6"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="52"/>
+    <x v="51"/>
+    <n v="13"/>
+    <n v="3.9"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="53"/>
+    <x v="52"/>
+    <n v="11"/>
+    <n v="4.0999999999999996"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="54"/>
+    <x v="53"/>
+    <n v="10"/>
+    <n v="4.3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="55"/>
+    <x v="54"/>
+    <n v="12"/>
+    <n v="4.5999999999999996"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="56"/>
+    <x v="55"/>
+    <n v="13"/>
+    <n v="4.9000000000000004"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Média"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="57"/>
+    <x v="56"/>
+    <n v="14"/>
+    <n v="5.2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="58"/>
+    <x v="57"/>
+    <n v="13"/>
+    <n v="5.4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Alta"/>
+    <s v="Sucesso"/>
+  </r>
+  <r>
+    <n v="59"/>
+    <x v="58"/>
+    <n v="15"/>
+    <n v="5.7"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Média"/>
+    <s v="Erro"/>
+  </r>
+  <r>
+    <n v="60"/>
+    <x v="59"/>
+    <n v="14"/>
+    <n v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Baixa"/>
+    <s v="Sucesso"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C87D6CF6-A735-424C-89A1-4135EC18ADE6}" name="Tabela dinâmica16" cacheId="44" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Prioridades">
+  <location ref="A29:B33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Contagem de Status" fld="7" subtotal="count" showDataAs="percentOfTotal" baseField="6" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <formats count="13">
+    <format dxfId="15">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F0DD972-7C08-484F-BF4D-38B843994521}" name="Tabela dinâmica40" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Região">
+  <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="FS" fld="5" subtotal="count" baseField="5" baseItem="0"/>
+    <dataField name="F%" fld="5" subtotal="count" showDataAs="percentOfTotal" baseField="5" baseItem="0" numFmtId="10"/>
+    <dataField name="FA" fld="5" subtotal="count" showDataAs="runTotal" baseField="5" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="82">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="81">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="80">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="79">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="78">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="77">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A788C7CA-0BF4-4F9F-A7C1-447EAA1A8214}" name="Tabela dinâmica46" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Prioridade">
+  <location ref="A3:D7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="FS" fld="6" subtotal="count" baseField="6" baseItem="0"/>
+    <dataField name="F%" fld="6" subtotal="count" showDataAs="percentOfTotal" baseField="6" baseItem="0" numFmtId="10"/>
+    <dataField name="FA" fld="6" subtotal="count" showDataAs="runTotal" baseField="6" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="76">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="75">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="74">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="73">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="72">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="71">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{323B8CD7-1EBF-4D0C-BC36-A5E1722D2E3F}" name="Tabela dinâmica58" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
+  <location ref="A3:D6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="FS" fld="7" subtotal="count" baseField="7" baseItem="0"/>
+    <dataField name="F%" fld="7" subtotal="count" showDataAs="percentOfTotal" baseField="7" baseItem="0" numFmtId="10"/>
+    <dataField name="FA" fld="7" subtotal="count" showDataAs="runTotal" baseField="7" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="70">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="69">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="68">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="67">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="66">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="65">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{783696FE-8BE0-4464-BDC4-2BE91AC1C4B9}" name="Tabela dinâmica13" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tipos de Usuários">
+  <location ref="A24:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média de Tempo_Resposta_ms" fld="1" subtotal="average" baseField="4" baseItem="0"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="27">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4E0D453-53CD-4006-BA8B-D1E3AAD2F39F}" name="Tabela dinâmica10" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Regiões">
+  <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Média de Tempo_Resposta_ms" fld="1" subtotal="average" baseField="5" baseItem="0"/>
+  </dataFields>
+  <formats count="13">
+    <format dxfId="31">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="33">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="37">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="38">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="39">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="40">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="41">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3BE27E52-3447-4DA8-A15E-1FE67D777079}" name="Tabela dinâmica7" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tipos de usuario">
+  <location ref="A12:C15" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Contagem de Tipo_Usuario" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Média de Tempo_Resposta_ms" fld="1" subtotal="average" baseField="4" baseItem="0"/>
+  </dataFields>
+  <formats count="13">
+    <format dxfId="43">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="48">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="49">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="51">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="52">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="53">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="54">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="29">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2C920598-30D1-4C5E-A133-9C4AA16CD70F}" name="Tabela dinâmica2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Regiões">
+  <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Contagem de Regiao" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="64">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="63">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="62">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="61">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="60">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="59">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="58">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="57">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="55">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BAE6BEF2-2551-46E7-AE50-4A4C60DCE74E}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo Resposta">
   <location ref="A3:D13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
@@ -20516,19 +25223,19 @@
     <dataField name="FA" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="51">
+    <format dxfId="116">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="115">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="114">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="113">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="112">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -20552,7 +25259,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C29BF07-BDDB-4534-AE0C-088EC7028C3F}" name="Tabela dinâmica12" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Requisição por Sessão">
   <location ref="A3:D20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
@@ -20669,19 +25376,19 @@
     <dataField name="FA" fld="2" subtotal="count" showDataAs="runTotal" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="11">
-    <format dxfId="46">
+    <format dxfId="111">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="110">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="109">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="108">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="107">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -20690,19 +25397,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="106">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="105">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="104">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="103">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="102">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -20711,7 +25418,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="36">
+    <format dxfId="101">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -20733,7 +25440,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BFB16522-CBC0-4805-A711-F81BE2F8A4C7}" name="Tabela dinâmica20" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tamanho Mb">
   <location ref="A3:D11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
@@ -20816,16 +25523,16 @@
     <dataField name="FA" fld="3" subtotal="count" showDataAs="runTotal" baseField="3" baseItem="1"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="35">
+    <format dxfId="100">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="99">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="98">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="97">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="7">
@@ -20840,10 +25547,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="95">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -20854,16 +25561,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="94">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="93">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="92">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="91">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="7">
@@ -20878,10 +25585,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="90">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="89">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -20905,7 +25612,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{248CD6D2-190F-4CD1-BCD7-1378B9688E1F}" name="Tabela dinâmica28" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tipo Usuário">
   <location ref="A3:D6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
@@ -20966,342 +25673,26 @@
     <dataField name="FA" fld="4" subtotal="count" showDataAs="runTotal" baseField="4" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="23">
+    <format dxfId="88">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="87">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="86">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="85">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="84">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="3">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F0DD972-7C08-484F-BF4D-38B843994521}" name="Tabela dinâmica40" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Região">
-  <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="FS" fld="5" subtotal="count" baseField="5" baseItem="0"/>
-    <dataField name="F%" fld="5" subtotal="count" showDataAs="percentOfTotal" baseField="5" baseItem="0" numFmtId="10"/>
-    <dataField name="FA" fld="5" subtotal="count" showDataAs="runTotal" baseField="5" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="17">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="16">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="3">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A788C7CA-0BF4-4F9F-A7C1-447EAA1A8214}" name="Tabela dinâmica46" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Prioridade">
-  <location ref="A3:D7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="FS" fld="6" subtotal="count" baseField="6" baseItem="0"/>
-    <dataField name="F%" fld="6" subtotal="count" showDataAs="percentOfTotal" baseField="6" baseItem="0" numFmtId="10"/>
-    <dataField name="FA" fld="6" subtotal="count" showDataAs="runTotal" baseField="6" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="11">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="3">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{323B8CD7-1EBF-4D0C-BC36-A5E1722D2E3F}" name="Tabela dinâmica58" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Status">
-  <location ref="A3:D6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="FS" fld="7" subtotal="count" baseField="7" baseItem="0"/>
-    <dataField name="F%" fld="7" subtotal="count" showDataAs="percentOfTotal" baseField="7" baseItem="0" numFmtId="10"/>
-    <dataField name="FA" fld="7" subtotal="count" showDataAs="runTotal" baseField="7" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="5">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="4">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="7" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
+    <format dxfId="83">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -21609,6 +26000,280 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D776DA32-6DE7-41D2-BAC8-E65CF58AC99E}">
+  <dimension ref="A3:D33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="27.36328125" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="9">
+        <v>5</v>
+      </c>
+      <c r="C5" s="9">
+        <v>5</v>
+      </c>
+      <c r="D5" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="9">
+        <v>6</v>
+      </c>
+      <c r="C6" s="9">
+        <v>4</v>
+      </c>
+      <c r="D6" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="9">
+        <v>4</v>
+      </c>
+      <c r="C7" s="9">
+        <v>18</v>
+      </c>
+      <c r="D7" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="9">
+        <v>3</v>
+      </c>
+      <c r="C8" s="9">
+        <v>15</v>
+      </c>
+      <c r="D8" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="9">
+        <v>18</v>
+      </c>
+      <c r="C9" s="9">
+        <v>42</v>
+      </c>
+      <c r="D9" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16">
+        <v>33</v>
+      </c>
+      <c r="C13" s="42">
+        <v>209.60606060606059</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="16">
+        <v>27</v>
+      </c>
+      <c r="C14" s="42">
+        <v>205.59259259259258</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="16">
+        <v>60</v>
+      </c>
+      <c r="C15" s="16">
+        <v>207.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="42">
+        <v>201.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="42">
+        <v>220.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="42">
+        <v>214.54545454545453</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="42">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="16">
+        <v>207.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="43">
+        <v>209.60606060606059</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="43">
+        <v>205.59259259259258</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="43">
+        <v>207.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="17">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="17">
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="17">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:Z66"/>
@@ -22984,10 +27649,10 @@
       <c r="H50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J50" s="37" t="s">
+      <c r="J50" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="K50" s="38"/>
+      <c r="K50" s="31"/>
       <c r="L50" s="4" t="s">
         <v>21</v>
       </c>
@@ -23044,10 +27709,10 @@
       <c r="H51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="30" t="s">
+      <c r="J51" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="K51" s="31"/>
+      <c r="K51" s="33"/>
       <c r="L51" s="6" t="s">
         <v>22</v>
       </c>
@@ -23060,27 +27725,27 @@
         <v>207.8</v>
       </c>
       <c r="Q51" s="34"/>
-      <c r="R51" s="35" t="e" cm="1">
+      <c r="R51" s="38" t="e" cm="1">
         <f t="array" ref="R51">_xlfn.MODE.MULT(B2:B61)</f>
         <v>#N/A</v>
       </c>
-      <c r="S51" s="36"/>
+      <c r="S51" s="39"/>
       <c r="T51" s="34">
         <f>MEDIAN(B2:B61)</f>
         <v>189</v>
       </c>
       <c r="U51" s="34"/>
-      <c r="V51" s="29">
+      <c r="V51" s="35">
         <f>_xlfn.VAR.S(B2:B61)</f>
         <v>4895.2135593220355</v>
       </c>
-      <c r="W51" s="29"/>
-      <c r="X51" s="29">
+      <c r="W51" s="35"/>
+      <c r="X51" s="35">
         <f>_xlfn.STDEV.S(B2:B61)</f>
         <v>69.965802784803628</v>
       </c>
-      <c r="Y51" s="29"/>
-      <c r="Z51" s="39">
+      <c r="Y51" s="35"/>
+      <c r="Z51" s="29">
         <f>X51/P51*100</f>
         <v>33.669779973437741</v>
       </c>
@@ -23110,10 +27775,10 @@
       <c r="H52" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J52" s="30" t="s">
+      <c r="J52" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="K52" s="31"/>
+      <c r="K52" s="33"/>
       <c r="L52" s="6" t="s">
         <v>21</v>
       </c>
@@ -23121,11 +27786,11 @@
         <v>54</v>
       </c>
       <c r="O52" s="34"/>
-      <c r="P52" s="29">
+      <c r="P52" s="35">
         <f>AVERAGE(C2:C61)</f>
         <v>8.4833333333333325</v>
       </c>
-      <c r="Q52" s="29"/>
+      <c r="Q52" s="35"/>
       <c r="R52" s="34" cm="1">
         <f t="array" ref="R52">_xlfn.MODE.MULT(C2:C61)</f>
         <v>7</v>
@@ -23136,17 +27801,17 @@
         <v>8</v>
       </c>
       <c r="U52" s="34"/>
-      <c r="V52" s="29">
+      <c r="V52" s="35">
         <f>_xlfn.VAR.S(C2:C61)</f>
         <v>17.135310734463282</v>
       </c>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29">
+      <c r="W52" s="35"/>
+      <c r="X52" s="35">
         <f>_xlfn.STDEV.S(C2:C61)</f>
         <v>4.1394819403475216</v>
       </c>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="39">
+      <c r="Y52" s="35"/>
+      <c r="Z52" s="29">
         <f>X52/P52*100</f>
         <v>48.79546491568788</v>
       </c>
@@ -23176,10 +27841,10 @@
       <c r="H53" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J53" s="30" t="s">
+      <c r="J53" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="K53" s="31"/>
+      <c r="K53" s="33"/>
       <c r="L53" s="6" t="s">
         <v>22</v>
       </c>
@@ -23187,11 +27852,11 @@
         <v>55</v>
       </c>
       <c r="O53" s="34"/>
-      <c r="P53" s="29">
+      <c r="P53" s="35">
         <f>AVERAGE(D2:D61)</f>
         <v>2.9283333333333332</v>
       </c>
-      <c r="Q53" s="29"/>
+      <c r="Q53" s="35"/>
       <c r="R53" s="27" cm="1">
         <f t="array" ref="R53:R66">_xlfn.MODE.MULT(D2:D61)</f>
         <v>1.2</v>
@@ -23202,17 +27867,17 @@
         <v>2.5</v>
       </c>
       <c r="U53" s="34"/>
-      <c r="V53" s="29">
+      <c r="V53" s="35">
         <f>_xlfn.VAR.S(D2:D61)</f>
         <v>3.4322344632768327</v>
       </c>
-      <c r="W53" s="29"/>
-      <c r="X53" s="29">
+      <c r="W53" s="35"/>
+      <c r="X53" s="35">
         <f>_xlfn.STDEV.S(D2:D61)</f>
         <v>1.8526290679131732</v>
       </c>
-      <c r="Y53" s="29"/>
-      <c r="Z53" s="39">
+      <c r="Y53" s="35"/>
+      <c r="Z53" s="29">
         <f>X53/P53*100</f>
         <v>63.26564830665361</v>
       </c>
@@ -23242,10 +27907,10 @@
       <c r="H54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J54" s="30" t="s">
+      <c r="J54" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="31"/>
+      <c r="K54" s="33"/>
       <c r="L54" s="6" t="s">
         <v>19</v>
       </c>
@@ -23278,10 +27943,10 @@
       <c r="H55" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J55" s="30" t="s">
+      <c r="J55" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="K55" s="31"/>
+      <c r="K55" s="33"/>
       <c r="L55" s="6" t="s">
         <v>19</v>
       </c>
@@ -23314,10 +27979,10 @@
       <c r="H56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J56" s="30" t="s">
+      <c r="J56" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="K56" s="31"/>
+      <c r="K56" s="33"/>
       <c r="L56" s="6" t="s">
         <v>20</v>
       </c>
@@ -23350,10 +28015,10 @@
       <c r="H57" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J57" s="32" t="s">
+      <c r="J57" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="K57" s="33"/>
+      <c r="K57" s="37"/>
       <c r="L57" s="7" t="s">
         <v>19</v>
       </c>
@@ -23504,12 +28169,15 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="X51:Y51"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="P52:Q52"/>
     <mergeCell ref="N50:O50"/>
     <mergeCell ref="X53:Y53"/>
     <mergeCell ref="T53:U53"/>
@@ -23526,15 +28194,12 @@
     <mergeCell ref="R50:S50"/>
     <mergeCell ref="T50:U50"/>
     <mergeCell ref="T51:U51"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="X51:Y51"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="J53:K53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23542,7 +28207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ACA1C58-9D91-4693-8874-FBEE7ADA22AA}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A3:F52"/>
@@ -23892,7 +28557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{685F8683-9FF2-4AB3-9FF9-EB87E5A7F84B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A3:D41"/>
@@ -24304,7 +28969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A2EACB-222A-43C4-B6B8-BE010F23FC67}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A3:D23"/>
@@ -24518,7 +29183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE94ACBA-5F69-4911-8427-0D54C30D4C0E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A3:D12"/>
@@ -24622,7 +29287,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10730F53-1099-459F-BE17-73BB8AB9D61F}">
   <sheetPr codeName="Planilha6"/>
   <dimension ref="A3:D16"/>
@@ -24770,7 +29435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADF40B5-799D-49EF-84DA-81B27C3CC8B3}">
   <sheetPr codeName="Planilha7"/>
   <dimension ref="A3:D14"/>
@@ -24896,7 +29561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81FF32B4-D917-47CD-8634-6912E0CE5486}">
   <sheetPr codeName="Planilha8"/>
   <dimension ref="A3:D12"/>
